--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -209,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -231,11 +231,55 @@
         <color rgb="00C0C0C0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C0C0C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C0C0C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -354,6 +398,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -740,6 +789,13 @@
           <t>《宗门论道》开发阶段规划（Godot引擎版）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="42" t="n"/>
+      <c r="G1" s="42" t="n"/>
+      <c r="H1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1201,6 +1257,11 @@
           <t>合计</t>
         </is>
       </c>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="43" t="n"/>
       <c r="G13" s="7">
         <f>SUM(G3:G12)</f>
         <v/>
@@ -1240,6 +1301,7 @@
           <t>游戏设计思路</t>
         </is>
       </c>
+      <c r="B1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="41" t="inlineStr">
@@ -1401,6 +1463,20 @@
           <t>《宗门论道》开发主表（Godot GDScript版）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="42" t="n"/>
+      <c r="G1" s="42" t="n"/>
+      <c r="H1" s="42" t="n"/>
+      <c r="I1" s="42" t="n"/>
+      <c r="J1" s="42" t="n"/>
+      <c r="K1" s="42" t="n"/>
+      <c r="L1" s="42" t="n"/>
+      <c r="M1" s="42" t="n"/>
+      <c r="N1" s="42" t="n"/>
+      <c r="O1" s="43" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -1485,20 +1561,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
+      <c r="B3" s="42" t="n"/>
+      <c r="C3" s="42" t="n"/>
+      <c r="D3" s="42" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="42" t="n"/>
+      <c r="H3" s="42" t="n"/>
+      <c r="I3" s="42" t="n"/>
+      <c r="J3" s="42" t="n"/>
+      <c r="K3" s="42" t="n"/>
+      <c r="L3" s="42" t="n"/>
+      <c r="M3" s="42" t="n"/>
+      <c r="N3" s="42" t="n"/>
+      <c r="O3" s="43" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
@@ -1506,20 +1582,20 @@
           <t xml:space="preserve">    ▸ A1.主场景循环  [P1]</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="n"/>
-      <c r="O4" s="13" t="n"/>
+      <c r="B4" s="42" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+      <c r="N4" s="42" t="n"/>
+      <c r="O4" s="43" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -1590,9 +1666,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O5" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -1815,9 +1891,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O8" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -1827,20 +1903,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="42" t="n"/>
+      <c r="I9" s="42" t="n"/>
+      <c r="J9" s="42" t="n"/>
+      <c r="K9" s="42" t="n"/>
+      <c r="L9" s="42" t="n"/>
+      <c r="M9" s="42" t="n"/>
+      <c r="N9" s="42" t="n"/>
+      <c r="O9" s="43" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1848,20 +1924,20 @@
           <t xml:space="preserve">    ▸ A2.输入系统  [P1]</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="42" t="n"/>
+      <c r="I10" s="42" t="n"/>
+      <c r="J10" s="42" t="n"/>
+      <c r="K10" s="42" t="n"/>
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="42" t="n"/>
+      <c r="N10" s="42" t="n"/>
+      <c r="O10" s="43" t="n"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -1932,9 +2008,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O11" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2007,9 +2083,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O12" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2082,9 +2158,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O13" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2157,9 +2233,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O14" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2169,20 +2245,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="42" t="n"/>
+      <c r="J15" s="42" t="n"/>
+      <c r="K15" s="42" t="n"/>
+      <c r="L15" s="42" t="n"/>
+      <c r="M15" s="42" t="n"/>
+      <c r="N15" s="42" t="n"/>
+      <c r="O15" s="43" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -2190,20 +2266,20 @@
           <t xml:space="preserve">    ▸ A3.事件总线  [P1]</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="42" t="n"/>
+      <c r="I16" s="42" t="n"/>
+      <c r="J16" s="42" t="n"/>
+      <c r="K16" s="42" t="n"/>
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="42" t="n"/>
+      <c r="N16" s="42" t="n"/>
+      <c r="O16" s="43" t="n"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
@@ -2274,9 +2350,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O17" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2349,9 +2425,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O18" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O18" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2424,9 +2500,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O19" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2436,20 +2512,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="11" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="42" t="n"/>
+      <c r="O20" s="43" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -2457,20 +2533,20 @@
           <t xml:space="preserve">    ▸ A4.场景管理  [P1]</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="13" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="42" t="n"/>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="42" t="n"/>
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="42" t="n"/>
+      <c r="N21" s="42" t="n"/>
+      <c r="O21" s="43" t="n"/>
     </row>
     <row r="22" ht="38" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
@@ -2541,9 +2617,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O22" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O22" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2616,9 +2692,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O23" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2628,20 +2704,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="11" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="42" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="42" t="n"/>
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="42" t="n"/>
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="42" t="n"/>
+      <c r="O24" s="43" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -2649,20 +2725,20 @@
           <t xml:space="preserve">    ▸ A5.渲染辅助  [P1]</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="13" t="n"/>
-      <c r="O25" s="13" t="n"/>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="42" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="42" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="42" t="n"/>
+      <c r="O25" s="43" t="n"/>
     </row>
     <row r="26" ht="38" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
@@ -2895,20 +2971,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="42" t="n"/>
+      <c r="L29" s="42" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="42" t="n"/>
+      <c r="O29" s="43" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -2916,20 +2992,20 @@
           <t xml:space="preserve">    ▸ A6.粒子系统  [P6]</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="13" t="n"/>
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="42" t="n"/>
+      <c r="H30" s="42" t="n"/>
+      <c r="I30" s="42" t="n"/>
+      <c r="J30" s="42" t="n"/>
+      <c r="K30" s="42" t="n"/>
+      <c r="L30" s="42" t="n"/>
+      <c r="M30" s="42" t="n"/>
+      <c r="N30" s="42" t="n"/>
+      <c r="O30" s="43" t="n"/>
     </row>
     <row r="31" ht="54" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
@@ -3087,20 +3163,20 @@
           <t xml:space="preserve">  A.项目骨架</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="42" t="n"/>
+      <c r="H33" s="42" t="n"/>
+      <c r="I33" s="42" t="n"/>
+      <c r="J33" s="42" t="n"/>
+      <c r="K33" s="42" t="n"/>
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="42" t="n"/>
+      <c r="N33" s="42" t="n"/>
+      <c r="O33" s="43" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -3108,20 +3184,20 @@
           <t xml:space="preserve">    ▸ A7.音频管理  [P6]</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="42" t="n"/>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="42" t="n"/>
+      <c r="J34" s="42" t="n"/>
+      <c r="K34" s="42" t="n"/>
+      <c r="L34" s="42" t="n"/>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="42" t="n"/>
+      <c r="O34" s="43" t="n"/>
     </row>
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
@@ -3279,20 +3355,20 @@
           <t xml:space="preserve">  B.游戏数据</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11" t="n"/>
+      <c r="B37" s="42" t="n"/>
+      <c r="C37" s="42" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="42" t="n"/>
+      <c r="H37" s="42" t="n"/>
+      <c r="I37" s="42" t="n"/>
+      <c r="J37" s="42" t="n"/>
+      <c r="K37" s="42" t="n"/>
+      <c r="L37" s="42" t="n"/>
+      <c r="M37" s="42" t="n"/>
+      <c r="N37" s="42" t="n"/>
+      <c r="O37" s="43" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -3300,20 +3376,20 @@
           <t xml:space="preserve">    ▸ B1.常量配置  [P2]</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="13" t="n"/>
-      <c r="O38" s="13" t="n"/>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="42" t="n"/>
+      <c r="H38" s="42" t="n"/>
+      <c r="I38" s="42" t="n"/>
+      <c r="J38" s="42" t="n"/>
+      <c r="K38" s="42" t="n"/>
+      <c r="L38" s="42" t="n"/>
+      <c r="M38" s="42" t="n"/>
+      <c r="N38" s="42" t="n"/>
+      <c r="O38" s="43" t="n"/>
     </row>
     <row r="39" ht="38" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
@@ -3396,20 +3472,20 @@
           <t xml:space="preserve">  B.游戏数据</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="11" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="11" t="n"/>
-      <c r="N40" s="11" t="n"/>
-      <c r="O40" s="11" t="n"/>
+      <c r="B40" s="42" t="n"/>
+      <c r="C40" s="42" t="n"/>
+      <c r="D40" s="42" t="n"/>
+      <c r="E40" s="42" t="n"/>
+      <c r="F40" s="42" t="n"/>
+      <c r="G40" s="42" t="n"/>
+      <c r="H40" s="42" t="n"/>
+      <c r="I40" s="42" t="n"/>
+      <c r="J40" s="42" t="n"/>
+      <c r="K40" s="42" t="n"/>
+      <c r="L40" s="42" t="n"/>
+      <c r="M40" s="42" t="n"/>
+      <c r="N40" s="42" t="n"/>
+      <c r="O40" s="43" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -3417,20 +3493,20 @@
           <t xml:space="preserve">    ▸ B2.卡牌数据表  [P2]</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="13" t="n"/>
-      <c r="N41" s="13" t="n"/>
-      <c r="O41" s="13" t="n"/>
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="42" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="42" t="n"/>
+      <c r="F41" s="42" t="n"/>
+      <c r="G41" s="42" t="n"/>
+      <c r="H41" s="42" t="n"/>
+      <c r="I41" s="42" t="n"/>
+      <c r="J41" s="42" t="n"/>
+      <c r="K41" s="42" t="n"/>
+      <c r="L41" s="42" t="n"/>
+      <c r="M41" s="42" t="n"/>
+      <c r="N41" s="42" t="n"/>
+      <c r="O41" s="43" t="n"/>
     </row>
     <row r="42" ht="38" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
@@ -3588,20 +3664,20 @@
           <t xml:space="preserve">  B.游戏数据</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="11" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
-      <c r="N44" s="11" t="n"/>
-      <c r="O44" s="11" t="n"/>
+      <c r="B44" s="42" t="n"/>
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="42" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="42" t="n"/>
+      <c r="H44" s="42" t="n"/>
+      <c r="I44" s="42" t="n"/>
+      <c r="J44" s="42" t="n"/>
+      <c r="K44" s="42" t="n"/>
+      <c r="L44" s="42" t="n"/>
+      <c r="M44" s="42" t="n"/>
+      <c r="N44" s="42" t="n"/>
+      <c r="O44" s="43" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
@@ -3609,20 +3685,20 @@
           <t xml:space="preserve">    ▸ B3.卡组手牌  [P2]</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="13" t="n"/>
-      <c r="N45" s="13" t="n"/>
-      <c r="O45" s="13" t="n"/>
+      <c r="B45" s="42" t="n"/>
+      <c r="C45" s="42" t="n"/>
+      <c r="D45" s="42" t="n"/>
+      <c r="E45" s="42" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="42" t="n"/>
+      <c r="I45" s="42" t="n"/>
+      <c r="J45" s="42" t="n"/>
+      <c r="K45" s="42" t="n"/>
+      <c r="L45" s="42" t="n"/>
+      <c r="M45" s="42" t="n"/>
+      <c r="N45" s="42" t="n"/>
+      <c r="O45" s="43" t="n"/>
     </row>
     <row r="46" ht="38" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
@@ -4080,20 +4156,20 @@
           <t xml:space="preserve">  B.游戏数据</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="11" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="11" t="n"/>
-      <c r="I52" s="11" t="n"/>
-      <c r="J52" s="11" t="n"/>
-      <c r="K52" s="11" t="n"/>
-      <c r="L52" s="11" t="n"/>
-      <c r="M52" s="11" t="n"/>
-      <c r="N52" s="11" t="n"/>
-      <c r="O52" s="11" t="n"/>
+      <c r="B52" s="42" t="n"/>
+      <c r="C52" s="42" t="n"/>
+      <c r="D52" s="42" t="n"/>
+      <c r="E52" s="42" t="n"/>
+      <c r="F52" s="42" t="n"/>
+      <c r="G52" s="42" t="n"/>
+      <c r="H52" s="42" t="n"/>
+      <c r="I52" s="42" t="n"/>
+      <c r="J52" s="42" t="n"/>
+      <c r="K52" s="42" t="n"/>
+      <c r="L52" s="42" t="n"/>
+      <c r="M52" s="42" t="n"/>
+      <c r="N52" s="42" t="n"/>
+      <c r="O52" s="43" t="n"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
@@ -4101,20 +4177,20 @@
           <t xml:space="preserve">    ▸ B4.预设卡组  [P2]</t>
         </is>
       </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
-      <c r="I53" s="13" t="n"/>
-      <c r="J53" s="13" t="n"/>
-      <c r="K53" s="13" t="n"/>
-      <c r="L53" s="13" t="n"/>
-      <c r="M53" s="13" t="n"/>
-      <c r="N53" s="13" t="n"/>
-      <c r="O53" s="13" t="n"/>
+      <c r="B53" s="42" t="n"/>
+      <c r="C53" s="42" t="n"/>
+      <c r="D53" s="42" t="n"/>
+      <c r="E53" s="42" t="n"/>
+      <c r="F53" s="42" t="n"/>
+      <c r="G53" s="42" t="n"/>
+      <c r="H53" s="42" t="n"/>
+      <c r="I53" s="42" t="n"/>
+      <c r="J53" s="42" t="n"/>
+      <c r="K53" s="42" t="n"/>
+      <c r="L53" s="42" t="n"/>
+      <c r="M53" s="42" t="n"/>
+      <c r="N53" s="42" t="n"/>
+      <c r="O53" s="43" t="n"/>
     </row>
     <row r="54" ht="54" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
@@ -4197,20 +4273,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="11" t="n"/>
-      <c r="K55" s="11" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="11" t="n"/>
+      <c r="B55" s="42" t="n"/>
+      <c r="C55" s="42" t="n"/>
+      <c r="D55" s="42" t="n"/>
+      <c r="E55" s="42" t="n"/>
+      <c r="F55" s="42" t="n"/>
+      <c r="G55" s="42" t="n"/>
+      <c r="H55" s="42" t="n"/>
+      <c r="I55" s="42" t="n"/>
+      <c r="J55" s="42" t="n"/>
+      <c r="K55" s="42" t="n"/>
+      <c r="L55" s="42" t="n"/>
+      <c r="M55" s="42" t="n"/>
+      <c r="N55" s="42" t="n"/>
+      <c r="O55" s="43" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
@@ -4218,20 +4294,20 @@
           <t xml:space="preserve">    ▸ C1.战斗主循环  [P3]</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
-      <c r="J56" s="13" t="n"/>
-      <c r="K56" s="13" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="13" t="n"/>
-      <c r="N56" s="13" t="n"/>
-      <c r="O56" s="13" t="n"/>
+      <c r="B56" s="42" t="n"/>
+      <c r="C56" s="42" t="n"/>
+      <c r="D56" s="42" t="n"/>
+      <c r="E56" s="42" t="n"/>
+      <c r="F56" s="42" t="n"/>
+      <c r="G56" s="42" t="n"/>
+      <c r="H56" s="42" t="n"/>
+      <c r="I56" s="42" t="n"/>
+      <c r="J56" s="42" t="n"/>
+      <c r="K56" s="42" t="n"/>
+      <c r="L56" s="42" t="n"/>
+      <c r="M56" s="42" t="n"/>
+      <c r="N56" s="42" t="n"/>
+      <c r="O56" s="43" t="n"/>
     </row>
     <row r="57" ht="70" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
@@ -4314,20 +4390,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="11" t="n"/>
-      <c r="F58" s="11" t="n"/>
-      <c r="G58" s="11" t="n"/>
-      <c r="H58" s="11" t="n"/>
-      <c r="I58" s="11" t="n"/>
-      <c r="J58" s="11" t="n"/>
-      <c r="K58" s="11" t="n"/>
-      <c r="L58" s="11" t="n"/>
-      <c r="M58" s="11" t="n"/>
-      <c r="N58" s="11" t="n"/>
-      <c r="O58" s="11" t="n"/>
+      <c r="B58" s="42" t="n"/>
+      <c r="C58" s="42" t="n"/>
+      <c r="D58" s="42" t="n"/>
+      <c r="E58" s="42" t="n"/>
+      <c r="F58" s="42" t="n"/>
+      <c r="G58" s="42" t="n"/>
+      <c r="H58" s="42" t="n"/>
+      <c r="I58" s="42" t="n"/>
+      <c r="J58" s="42" t="n"/>
+      <c r="K58" s="42" t="n"/>
+      <c r="L58" s="42" t="n"/>
+      <c r="M58" s="42" t="n"/>
+      <c r="N58" s="42" t="n"/>
+      <c r="O58" s="43" t="n"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
@@ -4335,20 +4411,20 @@
           <t xml:space="preserve">    ▸ C2.单位实体  [P3]</t>
         </is>
       </c>
-      <c r="B59" s="13" t="n"/>
-      <c r="C59" s="13" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="13" t="n"/>
-      <c r="H59" s="13" t="n"/>
-      <c r="I59" s="13" t="n"/>
-      <c r="J59" s="13" t="n"/>
-      <c r="K59" s="13" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
-      <c r="N59" s="13" t="n"/>
-      <c r="O59" s="13" t="n"/>
+      <c r="B59" s="42" t="n"/>
+      <c r="C59" s="42" t="n"/>
+      <c r="D59" s="42" t="n"/>
+      <c r="E59" s="42" t="n"/>
+      <c r="F59" s="42" t="n"/>
+      <c r="G59" s="42" t="n"/>
+      <c r="H59" s="42" t="n"/>
+      <c r="I59" s="42" t="n"/>
+      <c r="J59" s="42" t="n"/>
+      <c r="K59" s="42" t="n"/>
+      <c r="L59" s="42" t="n"/>
+      <c r="M59" s="42" t="n"/>
+      <c r="N59" s="42" t="n"/>
+      <c r="O59" s="43" t="n"/>
     </row>
     <row r="60" ht="54" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
@@ -4656,20 +4732,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n"/>
-      <c r="C64" s="11" t="n"/>
-      <c r="D64" s="11" t="n"/>
-      <c r="E64" s="11" t="n"/>
-      <c r="F64" s="11" t="n"/>
-      <c r="G64" s="11" t="n"/>
-      <c r="H64" s="11" t="n"/>
-      <c r="I64" s="11" t="n"/>
-      <c r="J64" s="11" t="n"/>
-      <c r="K64" s="11" t="n"/>
-      <c r="L64" s="11" t="n"/>
-      <c r="M64" s="11" t="n"/>
-      <c r="N64" s="11" t="n"/>
-      <c r="O64" s="11" t="n"/>
+      <c r="B64" s="42" t="n"/>
+      <c r="C64" s="42" t="n"/>
+      <c r="D64" s="42" t="n"/>
+      <c r="E64" s="42" t="n"/>
+      <c r="F64" s="42" t="n"/>
+      <c r="G64" s="42" t="n"/>
+      <c r="H64" s="42" t="n"/>
+      <c r="I64" s="42" t="n"/>
+      <c r="J64" s="42" t="n"/>
+      <c r="K64" s="42" t="n"/>
+      <c r="L64" s="42" t="n"/>
+      <c r="M64" s="42" t="n"/>
+      <c r="N64" s="42" t="n"/>
+      <c r="O64" s="43" t="n"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
@@ -4677,20 +4753,20 @@
           <t xml:space="preserve">    ▸ C3.移动系统  [P3]</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n"/>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="13" t="n"/>
-      <c r="H65" s="13" t="n"/>
-      <c r="I65" s="13" t="n"/>
-      <c r="J65" s="13" t="n"/>
-      <c r="K65" s="13" t="n"/>
-      <c r="L65" s="13" t="n"/>
-      <c r="M65" s="13" t="n"/>
-      <c r="N65" s="13" t="n"/>
-      <c r="O65" s="13" t="n"/>
+      <c r="B65" s="42" t="n"/>
+      <c r="C65" s="42" t="n"/>
+      <c r="D65" s="42" t="n"/>
+      <c r="E65" s="42" t="n"/>
+      <c r="F65" s="42" t="n"/>
+      <c r="G65" s="42" t="n"/>
+      <c r="H65" s="42" t="n"/>
+      <c r="I65" s="42" t="n"/>
+      <c r="J65" s="42" t="n"/>
+      <c r="K65" s="42" t="n"/>
+      <c r="L65" s="42" t="n"/>
+      <c r="M65" s="42" t="n"/>
+      <c r="N65" s="42" t="n"/>
+      <c r="O65" s="43" t="n"/>
     </row>
     <row r="66" ht="70" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
@@ -4998,20 +5074,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B70" s="11" t="n"/>
-      <c r="C70" s="11" t="n"/>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
-      <c r="G70" s="11" t="n"/>
-      <c r="H70" s="11" t="n"/>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="11" t="n"/>
-      <c r="K70" s="11" t="n"/>
-      <c r="L70" s="11" t="n"/>
-      <c r="M70" s="11" t="n"/>
-      <c r="N70" s="11" t="n"/>
-      <c r="O70" s="11" t="n"/>
+      <c r="B70" s="42" t="n"/>
+      <c r="C70" s="42" t="n"/>
+      <c r="D70" s="42" t="n"/>
+      <c r="E70" s="42" t="n"/>
+      <c r="F70" s="42" t="n"/>
+      <c r="G70" s="42" t="n"/>
+      <c r="H70" s="42" t="n"/>
+      <c r="I70" s="42" t="n"/>
+      <c r="J70" s="42" t="n"/>
+      <c r="K70" s="42" t="n"/>
+      <c r="L70" s="42" t="n"/>
+      <c r="M70" s="42" t="n"/>
+      <c r="N70" s="42" t="n"/>
+      <c r="O70" s="43" t="n"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
@@ -5019,20 +5095,20 @@
           <t xml:space="preserve">    ▸ C4.战斗系统  [P3]</t>
         </is>
       </c>
-      <c r="B71" s="13" t="n"/>
-      <c r="C71" s="13" t="n"/>
-      <c r="D71" s="13" t="n"/>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
-      <c r="G71" s="13" t="n"/>
-      <c r="H71" s="13" t="n"/>
-      <c r="I71" s="13" t="n"/>
-      <c r="J71" s="13" t="n"/>
-      <c r="K71" s="13" t="n"/>
-      <c r="L71" s="13" t="n"/>
-      <c r="M71" s="13" t="n"/>
-      <c r="N71" s="13" t="n"/>
-      <c r="O71" s="13" t="n"/>
+      <c r="B71" s="42" t="n"/>
+      <c r="C71" s="42" t="n"/>
+      <c r="D71" s="42" t="n"/>
+      <c r="E71" s="42" t="n"/>
+      <c r="F71" s="42" t="n"/>
+      <c r="G71" s="42" t="n"/>
+      <c r="H71" s="42" t="n"/>
+      <c r="I71" s="42" t="n"/>
+      <c r="J71" s="42" t="n"/>
+      <c r="K71" s="42" t="n"/>
+      <c r="L71" s="42" t="n"/>
+      <c r="M71" s="42" t="n"/>
+      <c r="N71" s="42" t="n"/>
+      <c r="O71" s="43" t="n"/>
     </row>
     <row r="72" ht="54" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
@@ -5490,20 +5566,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="11" t="n"/>
-      <c r="K78" s="11" t="n"/>
-      <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n"/>
-      <c r="O78" s="11" t="n"/>
+      <c r="B78" s="42" t="n"/>
+      <c r="C78" s="42" t="n"/>
+      <c r="D78" s="42" t="n"/>
+      <c r="E78" s="42" t="n"/>
+      <c r="F78" s="42" t="n"/>
+      <c r="G78" s="42" t="n"/>
+      <c r="H78" s="42" t="n"/>
+      <c r="I78" s="42" t="n"/>
+      <c r="J78" s="42" t="n"/>
+      <c r="K78" s="42" t="n"/>
+      <c r="L78" s="42" t="n"/>
+      <c r="M78" s="42" t="n"/>
+      <c r="N78" s="42" t="n"/>
+      <c r="O78" s="43" t="n"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
@@ -5511,20 +5587,20 @@
           <t xml:space="preserve">    ▸ C5.阵法系统  [P4]</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n"/>
-      <c r="C79" s="13" t="n"/>
-      <c r="D79" s="13" t="n"/>
-      <c r="E79" s="13" t="n"/>
-      <c r="F79" s="13" t="n"/>
-      <c r="G79" s="13" t="n"/>
-      <c r="H79" s="13" t="n"/>
-      <c r="I79" s="13" t="n"/>
-      <c r="J79" s="13" t="n"/>
-      <c r="K79" s="13" t="n"/>
-      <c r="L79" s="13" t="n"/>
-      <c r="M79" s="13" t="n"/>
-      <c r="N79" s="13" t="n"/>
-      <c r="O79" s="13" t="n"/>
+      <c r="B79" s="42" t="n"/>
+      <c r="C79" s="42" t="n"/>
+      <c r="D79" s="42" t="n"/>
+      <c r="E79" s="42" t="n"/>
+      <c r="F79" s="42" t="n"/>
+      <c r="G79" s="42" t="n"/>
+      <c r="H79" s="42" t="n"/>
+      <c r="I79" s="42" t="n"/>
+      <c r="J79" s="42" t="n"/>
+      <c r="K79" s="42" t="n"/>
+      <c r="L79" s="42" t="n"/>
+      <c r="M79" s="42" t="n"/>
+      <c r="N79" s="42" t="n"/>
+      <c r="O79" s="43" t="n"/>
     </row>
     <row r="80" ht="38" customHeight="1">
       <c r="A80" s="14" t="inlineStr">
@@ -5832,20 +5908,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B84" s="11" t="n"/>
-      <c r="C84" s="11" t="n"/>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="11" t="n"/>
-      <c r="F84" s="11" t="n"/>
-      <c r="G84" s="11" t="n"/>
-      <c r="H84" s="11" t="n"/>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="11" t="n"/>
-      <c r="K84" s="11" t="n"/>
-      <c r="L84" s="11" t="n"/>
-      <c r="M84" s="11" t="n"/>
-      <c r="N84" s="11" t="n"/>
-      <c r="O84" s="11" t="n"/>
+      <c r="B84" s="42" t="n"/>
+      <c r="C84" s="42" t="n"/>
+      <c r="D84" s="42" t="n"/>
+      <c r="E84" s="42" t="n"/>
+      <c r="F84" s="42" t="n"/>
+      <c r="G84" s="42" t="n"/>
+      <c r="H84" s="42" t="n"/>
+      <c r="I84" s="42" t="n"/>
+      <c r="J84" s="42" t="n"/>
+      <c r="K84" s="42" t="n"/>
+      <c r="L84" s="42" t="n"/>
+      <c r="M84" s="42" t="n"/>
+      <c r="N84" s="42" t="n"/>
+      <c r="O84" s="43" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="12" t="inlineStr">
@@ -5853,20 +5929,20 @@
           <t xml:space="preserve">    ▸ C6.法术系统  [P4]</t>
         </is>
       </c>
-      <c r="B85" s="13" t="n"/>
-      <c r="C85" s="13" t="n"/>
-      <c r="D85" s="13" t="n"/>
-      <c r="E85" s="13" t="n"/>
-      <c r="F85" s="13" t="n"/>
-      <c r="G85" s="13" t="n"/>
-      <c r="H85" s="13" t="n"/>
-      <c r="I85" s="13" t="n"/>
-      <c r="J85" s="13" t="n"/>
-      <c r="K85" s="13" t="n"/>
-      <c r="L85" s="13" t="n"/>
-      <c r="M85" s="13" t="n"/>
-      <c r="N85" s="13" t="n"/>
-      <c r="O85" s="13" t="n"/>
+      <c r="B85" s="42" t="n"/>
+      <c r="C85" s="42" t="n"/>
+      <c r="D85" s="42" t="n"/>
+      <c r="E85" s="42" t="n"/>
+      <c r="F85" s="42" t="n"/>
+      <c r="G85" s="42" t="n"/>
+      <c r="H85" s="42" t="n"/>
+      <c r="I85" s="42" t="n"/>
+      <c r="J85" s="42" t="n"/>
+      <c r="K85" s="42" t="n"/>
+      <c r="L85" s="42" t="n"/>
+      <c r="M85" s="42" t="n"/>
+      <c r="N85" s="42" t="n"/>
+      <c r="O85" s="43" t="n"/>
     </row>
     <row r="86" ht="54" customHeight="1">
       <c r="A86" s="14" t="inlineStr">
@@ -6549,20 +6625,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B95" s="11" t="n"/>
-      <c r="C95" s="11" t="n"/>
-      <c r="D95" s="11" t="n"/>
-      <c r="E95" s="11" t="n"/>
-      <c r="F95" s="11" t="n"/>
-      <c r="G95" s="11" t="n"/>
-      <c r="H95" s="11" t="n"/>
-      <c r="I95" s="11" t="n"/>
-      <c r="J95" s="11" t="n"/>
-      <c r="K95" s="11" t="n"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="11" t="n"/>
-      <c r="O95" s="11" t="n"/>
+      <c r="B95" s="42" t="n"/>
+      <c r="C95" s="42" t="n"/>
+      <c r="D95" s="42" t="n"/>
+      <c r="E95" s="42" t="n"/>
+      <c r="F95" s="42" t="n"/>
+      <c r="G95" s="42" t="n"/>
+      <c r="H95" s="42" t="n"/>
+      <c r="I95" s="42" t="n"/>
+      <c r="J95" s="42" t="n"/>
+      <c r="K95" s="42" t="n"/>
+      <c r="L95" s="42" t="n"/>
+      <c r="M95" s="42" t="n"/>
+      <c r="N95" s="42" t="n"/>
+      <c r="O95" s="43" t="n"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="12" t="inlineStr">
@@ -6570,20 +6646,20 @@
           <t xml:space="preserve">    ▸ C7.长老技能  [P4]</t>
         </is>
       </c>
-      <c r="B96" s="13" t="n"/>
-      <c r="C96" s="13" t="n"/>
-      <c r="D96" s="13" t="n"/>
-      <c r="E96" s="13" t="n"/>
-      <c r="F96" s="13" t="n"/>
-      <c r="G96" s="13" t="n"/>
-      <c r="H96" s="13" t="n"/>
-      <c r="I96" s="13" t="n"/>
-      <c r="J96" s="13" t="n"/>
-      <c r="K96" s="13" t="n"/>
-      <c r="L96" s="13" t="n"/>
-      <c r="M96" s="13" t="n"/>
-      <c r="N96" s="13" t="n"/>
-      <c r="O96" s="13" t="n"/>
+      <c r="B96" s="42" t="n"/>
+      <c r="C96" s="42" t="n"/>
+      <c r="D96" s="42" t="n"/>
+      <c r="E96" s="42" t="n"/>
+      <c r="F96" s="42" t="n"/>
+      <c r="G96" s="42" t="n"/>
+      <c r="H96" s="42" t="n"/>
+      <c r="I96" s="42" t="n"/>
+      <c r="J96" s="42" t="n"/>
+      <c r="K96" s="42" t="n"/>
+      <c r="L96" s="42" t="n"/>
+      <c r="M96" s="42" t="n"/>
+      <c r="N96" s="42" t="n"/>
+      <c r="O96" s="43" t="n"/>
     </row>
     <row r="97" ht="54" customHeight="1">
       <c r="A97" s="14" t="inlineStr">
@@ -7041,20 +7117,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B103" s="11" t="n"/>
-      <c r="C103" s="11" t="n"/>
-      <c r="D103" s="11" t="n"/>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="11" t="n"/>
-      <c r="G103" s="11" t="n"/>
-      <c r="H103" s="11" t="n"/>
-      <c r="I103" s="11" t="n"/>
-      <c r="J103" s="11" t="n"/>
-      <c r="K103" s="11" t="n"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
-      <c r="N103" s="11" t="n"/>
-      <c r="O103" s="11" t="n"/>
+      <c r="B103" s="42" t="n"/>
+      <c r="C103" s="42" t="n"/>
+      <c r="D103" s="42" t="n"/>
+      <c r="E103" s="42" t="n"/>
+      <c r="F103" s="42" t="n"/>
+      <c r="G103" s="42" t="n"/>
+      <c r="H103" s="42" t="n"/>
+      <c r="I103" s="42" t="n"/>
+      <c r="J103" s="42" t="n"/>
+      <c r="K103" s="42" t="n"/>
+      <c r="L103" s="42" t="n"/>
+      <c r="M103" s="42" t="n"/>
+      <c r="N103" s="42" t="n"/>
+      <c r="O103" s="43" t="n"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="12" t="inlineStr">
@@ -7062,20 +7138,20 @@
           <t xml:space="preserve">    ▸ C8.灵力系统  [P4]</t>
         </is>
       </c>
-      <c r="B104" s="13" t="n"/>
-      <c r="C104" s="13" t="n"/>
-      <c r="D104" s="13" t="n"/>
-      <c r="E104" s="13" t="n"/>
-      <c r="F104" s="13" t="n"/>
-      <c r="G104" s="13" t="n"/>
-      <c r="H104" s="13" t="n"/>
-      <c r="I104" s="13" t="n"/>
-      <c r="J104" s="13" t="n"/>
-      <c r="K104" s="13" t="n"/>
-      <c r="L104" s="13" t="n"/>
-      <c r="M104" s="13" t="n"/>
-      <c r="N104" s="13" t="n"/>
-      <c r="O104" s="13" t="n"/>
+      <c r="B104" s="42" t="n"/>
+      <c r="C104" s="42" t="n"/>
+      <c r="D104" s="42" t="n"/>
+      <c r="E104" s="42" t="n"/>
+      <c r="F104" s="42" t="n"/>
+      <c r="G104" s="42" t="n"/>
+      <c r="H104" s="42" t="n"/>
+      <c r="I104" s="42" t="n"/>
+      <c r="J104" s="42" t="n"/>
+      <c r="K104" s="42" t="n"/>
+      <c r="L104" s="42" t="n"/>
+      <c r="M104" s="42" t="n"/>
+      <c r="N104" s="42" t="n"/>
+      <c r="O104" s="43" t="n"/>
     </row>
     <row r="105" ht="70" customHeight="1">
       <c r="A105" s="14" t="inlineStr">
@@ -7233,20 +7309,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B107" s="11" t="n"/>
-      <c r="C107" s="11" t="n"/>
-      <c r="D107" s="11" t="n"/>
-      <c r="E107" s="11" t="n"/>
-      <c r="F107" s="11" t="n"/>
-      <c r="G107" s="11" t="n"/>
-      <c r="H107" s="11" t="n"/>
-      <c r="I107" s="11" t="n"/>
-      <c r="J107" s="11" t="n"/>
-      <c r="K107" s="11" t="n"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
-      <c r="N107" s="11" t="n"/>
-      <c r="O107" s="11" t="n"/>
+      <c r="B107" s="42" t="n"/>
+      <c r="C107" s="42" t="n"/>
+      <c r="D107" s="42" t="n"/>
+      <c r="E107" s="42" t="n"/>
+      <c r="F107" s="42" t="n"/>
+      <c r="G107" s="42" t="n"/>
+      <c r="H107" s="42" t="n"/>
+      <c r="I107" s="42" t="n"/>
+      <c r="J107" s="42" t="n"/>
+      <c r="K107" s="42" t="n"/>
+      <c r="L107" s="42" t="n"/>
+      <c r="M107" s="42" t="n"/>
+      <c r="N107" s="42" t="n"/>
+      <c r="O107" s="43" t="n"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="12" t="inlineStr">
@@ -7254,20 +7330,20 @@
           <t xml:space="preserve">    ▸ C9.出牌执行  [P4]</t>
         </is>
       </c>
-      <c r="B108" s="13" t="n"/>
-      <c r="C108" s="13" t="n"/>
-      <c r="D108" s="13" t="n"/>
-      <c r="E108" s="13" t="n"/>
-      <c r="F108" s="13" t="n"/>
-      <c r="G108" s="13" t="n"/>
-      <c r="H108" s="13" t="n"/>
-      <c r="I108" s="13" t="n"/>
-      <c r="J108" s="13" t="n"/>
-      <c r="K108" s="13" t="n"/>
-      <c r="L108" s="13" t="n"/>
-      <c r="M108" s="13" t="n"/>
-      <c r="N108" s="13" t="n"/>
-      <c r="O108" s="13" t="n"/>
+      <c r="B108" s="42" t="n"/>
+      <c r="C108" s="42" t="n"/>
+      <c r="D108" s="42" t="n"/>
+      <c r="E108" s="42" t="n"/>
+      <c r="F108" s="42" t="n"/>
+      <c r="G108" s="42" t="n"/>
+      <c r="H108" s="42" t="n"/>
+      <c r="I108" s="42" t="n"/>
+      <c r="J108" s="42" t="n"/>
+      <c r="K108" s="42" t="n"/>
+      <c r="L108" s="42" t="n"/>
+      <c r="M108" s="42" t="n"/>
+      <c r="N108" s="42" t="n"/>
+      <c r="O108" s="43" t="n"/>
     </row>
     <row r="109" ht="70" customHeight="1">
       <c r="A109" s="14" t="inlineStr">
@@ -7425,20 +7501,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B111" s="11" t="n"/>
-      <c r="C111" s="11" t="n"/>
-      <c r="D111" s="11" t="n"/>
-      <c r="E111" s="11" t="n"/>
-      <c r="F111" s="11" t="n"/>
-      <c r="G111" s="11" t="n"/>
-      <c r="H111" s="11" t="n"/>
-      <c r="I111" s="11" t="n"/>
-      <c r="J111" s="11" t="n"/>
-      <c r="K111" s="11" t="n"/>
-      <c r="L111" s="11" t="n"/>
-      <c r="M111" s="11" t="n"/>
-      <c r="N111" s="11" t="n"/>
-      <c r="O111" s="11" t="n"/>
+      <c r="B111" s="42" t="n"/>
+      <c r="C111" s="42" t="n"/>
+      <c r="D111" s="42" t="n"/>
+      <c r="E111" s="42" t="n"/>
+      <c r="F111" s="42" t="n"/>
+      <c r="G111" s="42" t="n"/>
+      <c r="H111" s="42" t="n"/>
+      <c r="I111" s="42" t="n"/>
+      <c r="J111" s="42" t="n"/>
+      <c r="K111" s="42" t="n"/>
+      <c r="L111" s="42" t="n"/>
+      <c r="M111" s="42" t="n"/>
+      <c r="N111" s="42" t="n"/>
+      <c r="O111" s="43" t="n"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="12" t="inlineStr">
@@ -7446,20 +7522,20 @@
           <t xml:space="preserve">    ▸ C10.胜负判定  [P3]</t>
         </is>
       </c>
-      <c r="B112" s="13" t="n"/>
-      <c r="C112" s="13" t="n"/>
-      <c r="D112" s="13" t="n"/>
-      <c r="E112" s="13" t="n"/>
-      <c r="F112" s="13" t="n"/>
-      <c r="G112" s="13" t="n"/>
-      <c r="H112" s="13" t="n"/>
-      <c r="I112" s="13" t="n"/>
-      <c r="J112" s="13" t="n"/>
-      <c r="K112" s="13" t="n"/>
-      <c r="L112" s="13" t="n"/>
-      <c r="M112" s="13" t="n"/>
-      <c r="N112" s="13" t="n"/>
-      <c r="O112" s="13" t="n"/>
+      <c r="B112" s="42" t="n"/>
+      <c r="C112" s="42" t="n"/>
+      <c r="D112" s="42" t="n"/>
+      <c r="E112" s="42" t="n"/>
+      <c r="F112" s="42" t="n"/>
+      <c r="G112" s="42" t="n"/>
+      <c r="H112" s="42" t="n"/>
+      <c r="I112" s="42" t="n"/>
+      <c r="J112" s="42" t="n"/>
+      <c r="K112" s="42" t="n"/>
+      <c r="L112" s="42" t="n"/>
+      <c r="M112" s="42" t="n"/>
+      <c r="N112" s="42" t="n"/>
+      <c r="O112" s="43" t="n"/>
     </row>
     <row r="113" ht="54" customHeight="1">
       <c r="A113" s="14" t="inlineStr">
@@ -7692,20 +7768,20 @@
           <t xml:space="preserve">  C.战斗逻辑</t>
         </is>
       </c>
-      <c r="B116" s="11" t="n"/>
-      <c r="C116" s="11" t="n"/>
-      <c r="D116" s="11" t="n"/>
-      <c r="E116" s="11" t="n"/>
-      <c r="F116" s="11" t="n"/>
-      <c r="G116" s="11" t="n"/>
-      <c r="H116" s="11" t="n"/>
-      <c r="I116" s="11" t="n"/>
-      <c r="J116" s="11" t="n"/>
-      <c r="K116" s="11" t="n"/>
-      <c r="L116" s="11" t="n"/>
-      <c r="M116" s="11" t="n"/>
-      <c r="N116" s="11" t="n"/>
-      <c r="O116" s="11" t="n"/>
+      <c r="B116" s="42" t="n"/>
+      <c r="C116" s="42" t="n"/>
+      <c r="D116" s="42" t="n"/>
+      <c r="E116" s="42" t="n"/>
+      <c r="F116" s="42" t="n"/>
+      <c r="G116" s="42" t="n"/>
+      <c r="H116" s="42" t="n"/>
+      <c r="I116" s="42" t="n"/>
+      <c r="J116" s="42" t="n"/>
+      <c r="K116" s="42" t="n"/>
+      <c r="L116" s="42" t="n"/>
+      <c r="M116" s="42" t="n"/>
+      <c r="N116" s="42" t="n"/>
+      <c r="O116" s="43" t="n"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="12" t="inlineStr">
@@ -7713,20 +7789,20 @@
           <t xml:space="preserve">    ▸ C11.死亡清理  [P3]</t>
         </is>
       </c>
-      <c r="B117" s="13" t="n"/>
-      <c r="C117" s="13" t="n"/>
-      <c r="D117" s="13" t="n"/>
-      <c r="E117" s="13" t="n"/>
-      <c r="F117" s="13" t="n"/>
-      <c r="G117" s="13" t="n"/>
-      <c r="H117" s="13" t="n"/>
-      <c r="I117" s="13" t="n"/>
-      <c r="J117" s="13" t="n"/>
-      <c r="K117" s="13" t="n"/>
-      <c r="L117" s="13" t="n"/>
-      <c r="M117" s="13" t="n"/>
-      <c r="N117" s="13" t="n"/>
-      <c r="O117" s="13" t="n"/>
+      <c r="B117" s="42" t="n"/>
+      <c r="C117" s="42" t="n"/>
+      <c r="D117" s="42" t="n"/>
+      <c r="E117" s="42" t="n"/>
+      <c r="F117" s="42" t="n"/>
+      <c r="G117" s="42" t="n"/>
+      <c r="H117" s="42" t="n"/>
+      <c r="I117" s="42" t="n"/>
+      <c r="J117" s="42" t="n"/>
+      <c r="K117" s="42" t="n"/>
+      <c r="L117" s="42" t="n"/>
+      <c r="M117" s="42" t="n"/>
+      <c r="N117" s="42" t="n"/>
+      <c r="O117" s="43" t="n"/>
     </row>
     <row r="118" ht="70" customHeight="1">
       <c r="A118" s="14" t="inlineStr">
@@ -7884,20 +7960,20 @@
           <t xml:space="preserve">  D.AI系统</t>
         </is>
       </c>
-      <c r="B120" s="11" t="n"/>
-      <c r="C120" s="11" t="n"/>
-      <c r="D120" s="11" t="n"/>
-      <c r="E120" s="11" t="n"/>
-      <c r="F120" s="11" t="n"/>
-      <c r="G120" s="11" t="n"/>
-      <c r="H120" s="11" t="n"/>
-      <c r="I120" s="11" t="n"/>
-      <c r="J120" s="11" t="n"/>
-      <c r="K120" s="11" t="n"/>
-      <c r="L120" s="11" t="n"/>
-      <c r="M120" s="11" t="n"/>
-      <c r="N120" s="11" t="n"/>
-      <c r="O120" s="11" t="n"/>
+      <c r="B120" s="42" t="n"/>
+      <c r="C120" s="42" t="n"/>
+      <c r="D120" s="42" t="n"/>
+      <c r="E120" s="42" t="n"/>
+      <c r="F120" s="42" t="n"/>
+      <c r="G120" s="42" t="n"/>
+      <c r="H120" s="42" t="n"/>
+      <c r="I120" s="42" t="n"/>
+      <c r="J120" s="42" t="n"/>
+      <c r="K120" s="42" t="n"/>
+      <c r="L120" s="42" t="n"/>
+      <c r="M120" s="42" t="n"/>
+      <c r="N120" s="42" t="n"/>
+      <c r="O120" s="43" t="n"/>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="12" t="inlineStr">
@@ -7905,20 +7981,20 @@
           <t xml:space="preserve">    ▸ D1.AI决策  [P5]</t>
         </is>
       </c>
-      <c r="B121" s="13" t="n"/>
-      <c r="C121" s="13" t="n"/>
-      <c r="D121" s="13" t="n"/>
-      <c r="E121" s="13" t="n"/>
-      <c r="F121" s="13" t="n"/>
-      <c r="G121" s="13" t="n"/>
-      <c r="H121" s="13" t="n"/>
-      <c r="I121" s="13" t="n"/>
-      <c r="J121" s="13" t="n"/>
-      <c r="K121" s="13" t="n"/>
-      <c r="L121" s="13" t="n"/>
-      <c r="M121" s="13" t="n"/>
-      <c r="N121" s="13" t="n"/>
-      <c r="O121" s="13" t="n"/>
+      <c r="B121" s="42" t="n"/>
+      <c r="C121" s="42" t="n"/>
+      <c r="D121" s="42" t="n"/>
+      <c r="E121" s="42" t="n"/>
+      <c r="F121" s="42" t="n"/>
+      <c r="G121" s="42" t="n"/>
+      <c r="H121" s="42" t="n"/>
+      <c r="I121" s="42" t="n"/>
+      <c r="J121" s="42" t="n"/>
+      <c r="K121" s="42" t="n"/>
+      <c r="L121" s="42" t="n"/>
+      <c r="M121" s="42" t="n"/>
+      <c r="N121" s="42" t="n"/>
+      <c r="O121" s="43" t="n"/>
     </row>
     <row r="122" ht="54" customHeight="1">
       <c r="A122" s="14" t="inlineStr">
@@ -8301,20 +8377,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B127" s="11" t="n"/>
-      <c r="C127" s="11" t="n"/>
-      <c r="D127" s="11" t="n"/>
-      <c r="E127" s="11" t="n"/>
-      <c r="F127" s="11" t="n"/>
-      <c r="G127" s="11" t="n"/>
-      <c r="H127" s="11" t="n"/>
-      <c r="I127" s="11" t="n"/>
-      <c r="J127" s="11" t="n"/>
-      <c r="K127" s="11" t="n"/>
-      <c r="L127" s="11" t="n"/>
-      <c r="M127" s="11" t="n"/>
-      <c r="N127" s="11" t="n"/>
-      <c r="O127" s="11" t="n"/>
+      <c r="B127" s="42" t="n"/>
+      <c r="C127" s="42" t="n"/>
+      <c r="D127" s="42" t="n"/>
+      <c r="E127" s="42" t="n"/>
+      <c r="F127" s="42" t="n"/>
+      <c r="G127" s="42" t="n"/>
+      <c r="H127" s="42" t="n"/>
+      <c r="I127" s="42" t="n"/>
+      <c r="J127" s="42" t="n"/>
+      <c r="K127" s="42" t="n"/>
+      <c r="L127" s="42" t="n"/>
+      <c r="M127" s="42" t="n"/>
+      <c r="N127" s="42" t="n"/>
+      <c r="O127" s="43" t="n"/>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
@@ -8322,20 +8398,20 @@
           <t xml:space="preserve">    ▸ E1.战斗场景  [P6]</t>
         </is>
       </c>
-      <c r="B128" s="13" t="n"/>
-      <c r="C128" s="13" t="n"/>
-      <c r="D128" s="13" t="n"/>
-      <c r="E128" s="13" t="n"/>
-      <c r="F128" s="13" t="n"/>
-      <c r="G128" s="13" t="n"/>
-      <c r="H128" s="13" t="n"/>
-      <c r="I128" s="13" t="n"/>
-      <c r="J128" s="13" t="n"/>
-      <c r="K128" s="13" t="n"/>
-      <c r="L128" s="13" t="n"/>
-      <c r="M128" s="13" t="n"/>
-      <c r="N128" s="13" t="n"/>
-      <c r="O128" s="13" t="n"/>
+      <c r="B128" s="42" t="n"/>
+      <c r="C128" s="42" t="n"/>
+      <c r="D128" s="42" t="n"/>
+      <c r="E128" s="42" t="n"/>
+      <c r="F128" s="42" t="n"/>
+      <c r="G128" s="42" t="n"/>
+      <c r="H128" s="42" t="n"/>
+      <c r="I128" s="42" t="n"/>
+      <c r="J128" s="42" t="n"/>
+      <c r="K128" s="42" t="n"/>
+      <c r="L128" s="42" t="n"/>
+      <c r="M128" s="42" t="n"/>
+      <c r="N128" s="42" t="n"/>
+      <c r="O128" s="43" t="n"/>
     </row>
     <row r="129" ht="54" customHeight="1">
       <c r="A129" s="14" t="inlineStr">
@@ -8643,20 +8719,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B133" s="11" t="n"/>
-      <c r="C133" s="11" t="n"/>
-      <c r="D133" s="11" t="n"/>
-      <c r="E133" s="11" t="n"/>
-      <c r="F133" s="11" t="n"/>
-      <c r="G133" s="11" t="n"/>
-      <c r="H133" s="11" t="n"/>
-      <c r="I133" s="11" t="n"/>
-      <c r="J133" s="11" t="n"/>
-      <c r="K133" s="11" t="n"/>
-      <c r="L133" s="11" t="n"/>
-      <c r="M133" s="11" t="n"/>
-      <c r="N133" s="11" t="n"/>
-      <c r="O133" s="11" t="n"/>
+      <c r="B133" s="42" t="n"/>
+      <c r="C133" s="42" t="n"/>
+      <c r="D133" s="42" t="n"/>
+      <c r="E133" s="42" t="n"/>
+      <c r="F133" s="42" t="n"/>
+      <c r="G133" s="42" t="n"/>
+      <c r="H133" s="42" t="n"/>
+      <c r="I133" s="42" t="n"/>
+      <c r="J133" s="42" t="n"/>
+      <c r="K133" s="42" t="n"/>
+      <c r="L133" s="42" t="n"/>
+      <c r="M133" s="42" t="n"/>
+      <c r="N133" s="42" t="n"/>
+      <c r="O133" s="43" t="n"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="12" t="inlineStr">
@@ -8664,20 +8740,20 @@
           <t xml:space="preserve">    ▸ E2.背景渲染  [P6]</t>
         </is>
       </c>
-      <c r="B134" s="13" t="n"/>
-      <c r="C134" s="13" t="n"/>
-      <c r="D134" s="13" t="n"/>
-      <c r="E134" s="13" t="n"/>
-      <c r="F134" s="13" t="n"/>
-      <c r="G134" s="13" t="n"/>
-      <c r="H134" s="13" t="n"/>
-      <c r="I134" s="13" t="n"/>
-      <c r="J134" s="13" t="n"/>
-      <c r="K134" s="13" t="n"/>
-      <c r="L134" s="13" t="n"/>
-      <c r="M134" s="13" t="n"/>
-      <c r="N134" s="13" t="n"/>
-      <c r="O134" s="13" t="n"/>
+      <c r="B134" s="42" t="n"/>
+      <c r="C134" s="42" t="n"/>
+      <c r="D134" s="42" t="n"/>
+      <c r="E134" s="42" t="n"/>
+      <c r="F134" s="42" t="n"/>
+      <c r="G134" s="42" t="n"/>
+      <c r="H134" s="42" t="n"/>
+      <c r="I134" s="42" t="n"/>
+      <c r="J134" s="42" t="n"/>
+      <c r="K134" s="42" t="n"/>
+      <c r="L134" s="42" t="n"/>
+      <c r="M134" s="42" t="n"/>
+      <c r="N134" s="42" t="n"/>
+      <c r="O134" s="43" t="n"/>
     </row>
     <row r="135" ht="38" customHeight="1">
       <c r="A135" s="14" t="inlineStr">
@@ -8835,20 +8911,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B137" s="11" t="n"/>
-      <c r="C137" s="11" t="n"/>
-      <c r="D137" s="11" t="n"/>
-      <c r="E137" s="11" t="n"/>
-      <c r="F137" s="11" t="n"/>
-      <c r="G137" s="11" t="n"/>
-      <c r="H137" s="11" t="n"/>
-      <c r="I137" s="11" t="n"/>
-      <c r="J137" s="11" t="n"/>
-      <c r="K137" s="11" t="n"/>
-      <c r="L137" s="11" t="n"/>
-      <c r="M137" s="11" t="n"/>
-      <c r="N137" s="11" t="n"/>
-      <c r="O137" s="11" t="n"/>
+      <c r="B137" s="42" t="n"/>
+      <c r="C137" s="42" t="n"/>
+      <c r="D137" s="42" t="n"/>
+      <c r="E137" s="42" t="n"/>
+      <c r="F137" s="42" t="n"/>
+      <c r="G137" s="42" t="n"/>
+      <c r="H137" s="42" t="n"/>
+      <c r="I137" s="42" t="n"/>
+      <c r="J137" s="42" t="n"/>
+      <c r="K137" s="42" t="n"/>
+      <c r="L137" s="42" t="n"/>
+      <c r="M137" s="42" t="n"/>
+      <c r="N137" s="42" t="n"/>
+      <c r="O137" s="43" t="n"/>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="12" t="inlineStr">
@@ -8856,20 +8932,20 @@
           <t xml:space="preserve">    ▸ E3.大殿渲染  [P6]</t>
         </is>
       </c>
-      <c r="B138" s="13" t="n"/>
-      <c r="C138" s="13" t="n"/>
-      <c r="D138" s="13" t="n"/>
-      <c r="E138" s="13" t="n"/>
-      <c r="F138" s="13" t="n"/>
-      <c r="G138" s="13" t="n"/>
-      <c r="H138" s="13" t="n"/>
-      <c r="I138" s="13" t="n"/>
-      <c r="J138" s="13" t="n"/>
-      <c r="K138" s="13" t="n"/>
-      <c r="L138" s="13" t="n"/>
-      <c r="M138" s="13" t="n"/>
-      <c r="N138" s="13" t="n"/>
-      <c r="O138" s="13" t="n"/>
+      <c r="B138" s="42" t="n"/>
+      <c r="C138" s="42" t="n"/>
+      <c r="D138" s="42" t="n"/>
+      <c r="E138" s="42" t="n"/>
+      <c r="F138" s="42" t="n"/>
+      <c r="G138" s="42" t="n"/>
+      <c r="H138" s="42" t="n"/>
+      <c r="I138" s="42" t="n"/>
+      <c r="J138" s="42" t="n"/>
+      <c r="K138" s="42" t="n"/>
+      <c r="L138" s="42" t="n"/>
+      <c r="M138" s="42" t="n"/>
+      <c r="N138" s="42" t="n"/>
+      <c r="O138" s="43" t="n"/>
     </row>
     <row r="139" ht="38" customHeight="1">
       <c r="A139" s="14" t="inlineStr">
@@ -9102,20 +9178,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B142" s="11" t="n"/>
-      <c r="C142" s="11" t="n"/>
-      <c r="D142" s="11" t="n"/>
-      <c r="E142" s="11" t="n"/>
-      <c r="F142" s="11" t="n"/>
-      <c r="G142" s="11" t="n"/>
-      <c r="H142" s="11" t="n"/>
-      <c r="I142" s="11" t="n"/>
-      <c r="J142" s="11" t="n"/>
-      <c r="K142" s="11" t="n"/>
-      <c r="L142" s="11" t="n"/>
-      <c r="M142" s="11" t="n"/>
-      <c r="N142" s="11" t="n"/>
-      <c r="O142" s="11" t="n"/>
+      <c r="B142" s="42" t="n"/>
+      <c r="C142" s="42" t="n"/>
+      <c r="D142" s="42" t="n"/>
+      <c r="E142" s="42" t="n"/>
+      <c r="F142" s="42" t="n"/>
+      <c r="G142" s="42" t="n"/>
+      <c r="H142" s="42" t="n"/>
+      <c r="I142" s="42" t="n"/>
+      <c r="J142" s="42" t="n"/>
+      <c r="K142" s="42" t="n"/>
+      <c r="L142" s="42" t="n"/>
+      <c r="M142" s="42" t="n"/>
+      <c r="N142" s="42" t="n"/>
+      <c r="O142" s="43" t="n"/>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="12" t="inlineStr">
@@ -9123,20 +9199,20 @@
           <t xml:space="preserve">    ▸ E4.单位渲染  [P6]</t>
         </is>
       </c>
-      <c r="B143" s="13" t="n"/>
-      <c r="C143" s="13" t="n"/>
-      <c r="D143" s="13" t="n"/>
-      <c r="E143" s="13" t="n"/>
-      <c r="F143" s="13" t="n"/>
-      <c r="G143" s="13" t="n"/>
-      <c r="H143" s="13" t="n"/>
-      <c r="I143" s="13" t="n"/>
-      <c r="J143" s="13" t="n"/>
-      <c r="K143" s="13" t="n"/>
-      <c r="L143" s="13" t="n"/>
-      <c r="M143" s="13" t="n"/>
-      <c r="N143" s="13" t="n"/>
-      <c r="O143" s="13" t="n"/>
+      <c r="B143" s="42" t="n"/>
+      <c r="C143" s="42" t="n"/>
+      <c r="D143" s="42" t="n"/>
+      <c r="E143" s="42" t="n"/>
+      <c r="F143" s="42" t="n"/>
+      <c r="G143" s="42" t="n"/>
+      <c r="H143" s="42" t="n"/>
+      <c r="I143" s="42" t="n"/>
+      <c r="J143" s="42" t="n"/>
+      <c r="K143" s="42" t="n"/>
+      <c r="L143" s="42" t="n"/>
+      <c r="M143" s="42" t="n"/>
+      <c r="N143" s="42" t="n"/>
+      <c r="O143" s="43" t="n"/>
     </row>
     <row r="144" ht="38" customHeight="1">
       <c r="A144" s="14" t="inlineStr">
@@ -9294,20 +9370,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B146" s="11" t="n"/>
-      <c r="C146" s="11" t="n"/>
-      <c r="D146" s="11" t="n"/>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="11" t="n"/>
-      <c r="G146" s="11" t="n"/>
-      <c r="H146" s="11" t="n"/>
-      <c r="I146" s="11" t="n"/>
-      <c r="J146" s="11" t="n"/>
-      <c r="K146" s="11" t="n"/>
-      <c r="L146" s="11" t="n"/>
-      <c r="M146" s="11" t="n"/>
-      <c r="N146" s="11" t="n"/>
-      <c r="O146" s="11" t="n"/>
+      <c r="B146" s="42" t="n"/>
+      <c r="C146" s="42" t="n"/>
+      <c r="D146" s="42" t="n"/>
+      <c r="E146" s="42" t="n"/>
+      <c r="F146" s="42" t="n"/>
+      <c r="G146" s="42" t="n"/>
+      <c r="H146" s="42" t="n"/>
+      <c r="I146" s="42" t="n"/>
+      <c r="J146" s="42" t="n"/>
+      <c r="K146" s="42" t="n"/>
+      <c r="L146" s="42" t="n"/>
+      <c r="M146" s="42" t="n"/>
+      <c r="N146" s="42" t="n"/>
+      <c r="O146" s="43" t="n"/>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="12" t="inlineStr">
@@ -9315,20 +9391,20 @@
           <t xml:space="preserve">    ▸ E5.阵法渲染  [P6]</t>
         </is>
       </c>
-      <c r="B147" s="13" t="n"/>
-      <c r="C147" s="13" t="n"/>
-      <c r="D147" s="13" t="n"/>
-      <c r="E147" s="13" t="n"/>
-      <c r="F147" s="13" t="n"/>
-      <c r="G147" s="13" t="n"/>
-      <c r="H147" s="13" t="n"/>
-      <c r="I147" s="13" t="n"/>
-      <c r="J147" s="13" t="n"/>
-      <c r="K147" s="13" t="n"/>
-      <c r="L147" s="13" t="n"/>
-      <c r="M147" s="13" t="n"/>
-      <c r="N147" s="13" t="n"/>
-      <c r="O147" s="13" t="n"/>
+      <c r="B147" s="42" t="n"/>
+      <c r="C147" s="42" t="n"/>
+      <c r="D147" s="42" t="n"/>
+      <c r="E147" s="42" t="n"/>
+      <c r="F147" s="42" t="n"/>
+      <c r="G147" s="42" t="n"/>
+      <c r="H147" s="42" t="n"/>
+      <c r="I147" s="42" t="n"/>
+      <c r="J147" s="42" t="n"/>
+      <c r="K147" s="42" t="n"/>
+      <c r="L147" s="42" t="n"/>
+      <c r="M147" s="42" t="n"/>
+      <c r="N147" s="42" t="n"/>
+      <c r="O147" s="43" t="n"/>
     </row>
     <row r="148" ht="38" customHeight="1">
       <c r="A148" s="14" t="inlineStr">
@@ -9411,20 +9487,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B149" s="11" t="n"/>
-      <c r="C149" s="11" t="n"/>
-      <c r="D149" s="11" t="n"/>
-      <c r="E149" s="11" t="n"/>
-      <c r="F149" s="11" t="n"/>
-      <c r="G149" s="11" t="n"/>
-      <c r="H149" s="11" t="n"/>
-      <c r="I149" s="11" t="n"/>
-      <c r="J149" s="11" t="n"/>
-      <c r="K149" s="11" t="n"/>
-      <c r="L149" s="11" t="n"/>
-      <c r="M149" s="11" t="n"/>
-      <c r="N149" s="11" t="n"/>
-      <c r="O149" s="11" t="n"/>
+      <c r="B149" s="42" t="n"/>
+      <c r="C149" s="42" t="n"/>
+      <c r="D149" s="42" t="n"/>
+      <c r="E149" s="42" t="n"/>
+      <c r="F149" s="42" t="n"/>
+      <c r="G149" s="42" t="n"/>
+      <c r="H149" s="42" t="n"/>
+      <c r="I149" s="42" t="n"/>
+      <c r="J149" s="42" t="n"/>
+      <c r="K149" s="42" t="n"/>
+      <c r="L149" s="42" t="n"/>
+      <c r="M149" s="42" t="n"/>
+      <c r="N149" s="42" t="n"/>
+      <c r="O149" s="43" t="n"/>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
@@ -9432,20 +9508,20 @@
           <t xml:space="preserve">    ▸ E6.UI-手牌栏  [P6]</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n"/>
-      <c r="C150" s="13" t="n"/>
-      <c r="D150" s="13" t="n"/>
-      <c r="E150" s="13" t="n"/>
-      <c r="F150" s="13" t="n"/>
-      <c r="G150" s="13" t="n"/>
-      <c r="H150" s="13" t="n"/>
-      <c r="I150" s="13" t="n"/>
-      <c r="J150" s="13" t="n"/>
-      <c r="K150" s="13" t="n"/>
-      <c r="L150" s="13" t="n"/>
-      <c r="M150" s="13" t="n"/>
-      <c r="N150" s="13" t="n"/>
-      <c r="O150" s="13" t="n"/>
+      <c r="B150" s="42" t="n"/>
+      <c r="C150" s="42" t="n"/>
+      <c r="D150" s="42" t="n"/>
+      <c r="E150" s="42" t="n"/>
+      <c r="F150" s="42" t="n"/>
+      <c r="G150" s="42" t="n"/>
+      <c r="H150" s="42" t="n"/>
+      <c r="I150" s="42" t="n"/>
+      <c r="J150" s="42" t="n"/>
+      <c r="K150" s="42" t="n"/>
+      <c r="L150" s="42" t="n"/>
+      <c r="M150" s="42" t="n"/>
+      <c r="N150" s="42" t="n"/>
+      <c r="O150" s="43" t="n"/>
     </row>
     <row r="151" ht="38" customHeight="1">
       <c r="A151" s="14" t="inlineStr">
@@ -9603,20 +9679,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B153" s="11" t="n"/>
-      <c r="C153" s="11" t="n"/>
-      <c r="D153" s="11" t="n"/>
-      <c r="E153" s="11" t="n"/>
-      <c r="F153" s="11" t="n"/>
-      <c r="G153" s="11" t="n"/>
-      <c r="H153" s="11" t="n"/>
-      <c r="I153" s="11" t="n"/>
-      <c r="J153" s="11" t="n"/>
-      <c r="K153" s="11" t="n"/>
-      <c r="L153" s="11" t="n"/>
-      <c r="M153" s="11" t="n"/>
-      <c r="N153" s="11" t="n"/>
-      <c r="O153" s="11" t="n"/>
+      <c r="B153" s="42" t="n"/>
+      <c r="C153" s="42" t="n"/>
+      <c r="D153" s="42" t="n"/>
+      <c r="E153" s="42" t="n"/>
+      <c r="F153" s="42" t="n"/>
+      <c r="G153" s="42" t="n"/>
+      <c r="H153" s="42" t="n"/>
+      <c r="I153" s="42" t="n"/>
+      <c r="J153" s="42" t="n"/>
+      <c r="K153" s="42" t="n"/>
+      <c r="L153" s="42" t="n"/>
+      <c r="M153" s="42" t="n"/>
+      <c r="N153" s="42" t="n"/>
+      <c r="O153" s="43" t="n"/>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
@@ -9624,20 +9700,20 @@
           <t xml:space="preserve">    ▸ E7.UI-灵力条  [P6]</t>
         </is>
       </c>
-      <c r="B154" s="13" t="n"/>
-      <c r="C154" s="13" t="n"/>
-      <c r="D154" s="13" t="n"/>
-      <c r="E154" s="13" t="n"/>
-      <c r="F154" s="13" t="n"/>
-      <c r="G154" s="13" t="n"/>
-      <c r="H154" s="13" t="n"/>
-      <c r="I154" s="13" t="n"/>
-      <c r="J154" s="13" t="n"/>
-      <c r="K154" s="13" t="n"/>
-      <c r="L154" s="13" t="n"/>
-      <c r="M154" s="13" t="n"/>
-      <c r="N154" s="13" t="n"/>
-      <c r="O154" s="13" t="n"/>
+      <c r="B154" s="42" t="n"/>
+      <c r="C154" s="42" t="n"/>
+      <c r="D154" s="42" t="n"/>
+      <c r="E154" s="42" t="n"/>
+      <c r="F154" s="42" t="n"/>
+      <c r="G154" s="42" t="n"/>
+      <c r="H154" s="42" t="n"/>
+      <c r="I154" s="42" t="n"/>
+      <c r="J154" s="42" t="n"/>
+      <c r="K154" s="42" t="n"/>
+      <c r="L154" s="42" t="n"/>
+      <c r="M154" s="42" t="n"/>
+      <c r="N154" s="42" t="n"/>
+      <c r="O154" s="43" t="n"/>
     </row>
     <row r="155" ht="38" customHeight="1">
       <c r="A155" s="14" t="inlineStr">
@@ -9720,20 +9796,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B156" s="11" t="n"/>
-      <c r="C156" s="11" t="n"/>
-      <c r="D156" s="11" t="n"/>
-      <c r="E156" s="11" t="n"/>
-      <c r="F156" s="11" t="n"/>
-      <c r="G156" s="11" t="n"/>
-      <c r="H156" s="11" t="n"/>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="11" t="n"/>
-      <c r="K156" s="11" t="n"/>
-      <c r="L156" s="11" t="n"/>
-      <c r="M156" s="11" t="n"/>
-      <c r="N156" s="11" t="n"/>
-      <c r="O156" s="11" t="n"/>
+      <c r="B156" s="42" t="n"/>
+      <c r="C156" s="42" t="n"/>
+      <c r="D156" s="42" t="n"/>
+      <c r="E156" s="42" t="n"/>
+      <c r="F156" s="42" t="n"/>
+      <c r="G156" s="42" t="n"/>
+      <c r="H156" s="42" t="n"/>
+      <c r="I156" s="42" t="n"/>
+      <c r="J156" s="42" t="n"/>
+      <c r="K156" s="42" t="n"/>
+      <c r="L156" s="42" t="n"/>
+      <c r="M156" s="42" t="n"/>
+      <c r="N156" s="42" t="n"/>
+      <c r="O156" s="43" t="n"/>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="12" t="inlineStr">
@@ -9741,20 +9817,20 @@
           <t xml:space="preserve">    ▸ E8.UI-顶部HUD  [P6]</t>
         </is>
       </c>
-      <c r="B157" s="13" t="n"/>
-      <c r="C157" s="13" t="n"/>
-      <c r="D157" s="13" t="n"/>
-      <c r="E157" s="13" t="n"/>
-      <c r="F157" s="13" t="n"/>
-      <c r="G157" s="13" t="n"/>
-      <c r="H157" s="13" t="n"/>
-      <c r="I157" s="13" t="n"/>
-      <c r="J157" s="13" t="n"/>
-      <c r="K157" s="13" t="n"/>
-      <c r="L157" s="13" t="n"/>
-      <c r="M157" s="13" t="n"/>
-      <c r="N157" s="13" t="n"/>
-      <c r="O157" s="13" t="n"/>
+      <c r="B157" s="42" t="n"/>
+      <c r="C157" s="42" t="n"/>
+      <c r="D157" s="42" t="n"/>
+      <c r="E157" s="42" t="n"/>
+      <c r="F157" s="42" t="n"/>
+      <c r="G157" s="42" t="n"/>
+      <c r="H157" s="42" t="n"/>
+      <c r="I157" s="42" t="n"/>
+      <c r="J157" s="42" t="n"/>
+      <c r="K157" s="42" t="n"/>
+      <c r="L157" s="42" t="n"/>
+      <c r="M157" s="42" t="n"/>
+      <c r="N157" s="42" t="n"/>
+      <c r="O157" s="43" t="n"/>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="14" t="inlineStr">
@@ -9912,20 +9988,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B160" s="11" t="n"/>
-      <c r="C160" s="11" t="n"/>
-      <c r="D160" s="11" t="n"/>
-      <c r="E160" s="11" t="n"/>
-      <c r="F160" s="11" t="n"/>
-      <c r="G160" s="11" t="n"/>
-      <c r="H160" s="11" t="n"/>
-      <c r="I160" s="11" t="n"/>
-      <c r="J160" s="11" t="n"/>
-      <c r="K160" s="11" t="n"/>
-      <c r="L160" s="11" t="n"/>
-      <c r="M160" s="11" t="n"/>
-      <c r="N160" s="11" t="n"/>
-      <c r="O160" s="11" t="n"/>
+      <c r="B160" s="42" t="n"/>
+      <c r="C160" s="42" t="n"/>
+      <c r="D160" s="42" t="n"/>
+      <c r="E160" s="42" t="n"/>
+      <c r="F160" s="42" t="n"/>
+      <c r="G160" s="42" t="n"/>
+      <c r="H160" s="42" t="n"/>
+      <c r="I160" s="42" t="n"/>
+      <c r="J160" s="42" t="n"/>
+      <c r="K160" s="42" t="n"/>
+      <c r="L160" s="42" t="n"/>
+      <c r="M160" s="42" t="n"/>
+      <c r="N160" s="42" t="n"/>
+      <c r="O160" s="43" t="n"/>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="12" t="inlineStr">
@@ -9933,20 +10009,20 @@
           <t xml:space="preserve">    ▸ E9.出牌交互  [P6]</t>
         </is>
       </c>
-      <c r="B161" s="13" t="n"/>
-      <c r="C161" s="13" t="n"/>
-      <c r="D161" s="13" t="n"/>
-      <c r="E161" s="13" t="n"/>
-      <c r="F161" s="13" t="n"/>
-      <c r="G161" s="13" t="n"/>
-      <c r="H161" s="13" t="n"/>
-      <c r="I161" s="13" t="n"/>
-      <c r="J161" s="13" t="n"/>
-      <c r="K161" s="13" t="n"/>
-      <c r="L161" s="13" t="n"/>
-      <c r="M161" s="13" t="n"/>
-      <c r="N161" s="13" t="n"/>
-      <c r="O161" s="13" t="n"/>
+      <c r="B161" s="42" t="n"/>
+      <c r="C161" s="42" t="n"/>
+      <c r="D161" s="42" t="n"/>
+      <c r="E161" s="42" t="n"/>
+      <c r="F161" s="42" t="n"/>
+      <c r="G161" s="42" t="n"/>
+      <c r="H161" s="42" t="n"/>
+      <c r="I161" s="42" t="n"/>
+      <c r="J161" s="42" t="n"/>
+      <c r="K161" s="42" t="n"/>
+      <c r="L161" s="42" t="n"/>
+      <c r="M161" s="42" t="n"/>
+      <c r="N161" s="42" t="n"/>
+      <c r="O161" s="43" t="n"/>
     </row>
     <row r="162" ht="54" customHeight="1">
       <c r="A162" s="14" t="inlineStr">
@@ -10104,20 +10180,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B164" s="11" t="n"/>
-      <c r="C164" s="11" t="n"/>
-      <c r="D164" s="11" t="n"/>
-      <c r="E164" s="11" t="n"/>
-      <c r="F164" s="11" t="n"/>
-      <c r="G164" s="11" t="n"/>
-      <c r="H164" s="11" t="n"/>
-      <c r="I164" s="11" t="n"/>
-      <c r="J164" s="11" t="n"/>
-      <c r="K164" s="11" t="n"/>
-      <c r="L164" s="11" t="n"/>
-      <c r="M164" s="11" t="n"/>
-      <c r="N164" s="11" t="n"/>
-      <c r="O164" s="11" t="n"/>
+      <c r="B164" s="42" t="n"/>
+      <c r="C164" s="42" t="n"/>
+      <c r="D164" s="42" t="n"/>
+      <c r="E164" s="42" t="n"/>
+      <c r="F164" s="42" t="n"/>
+      <c r="G164" s="42" t="n"/>
+      <c r="H164" s="42" t="n"/>
+      <c r="I164" s="42" t="n"/>
+      <c r="J164" s="42" t="n"/>
+      <c r="K164" s="42" t="n"/>
+      <c r="L164" s="42" t="n"/>
+      <c r="M164" s="42" t="n"/>
+      <c r="N164" s="42" t="n"/>
+      <c r="O164" s="43" t="n"/>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="12" t="inlineStr">
@@ -10125,20 +10201,20 @@
           <t xml:space="preserve">    ▸ E10.结算场景  [P6]</t>
         </is>
       </c>
-      <c r="B165" s="13" t="n"/>
-      <c r="C165" s="13" t="n"/>
-      <c r="D165" s="13" t="n"/>
-      <c r="E165" s="13" t="n"/>
-      <c r="F165" s="13" t="n"/>
-      <c r="G165" s="13" t="n"/>
-      <c r="H165" s="13" t="n"/>
-      <c r="I165" s="13" t="n"/>
-      <c r="J165" s="13" t="n"/>
-      <c r="K165" s="13" t="n"/>
-      <c r="L165" s="13" t="n"/>
-      <c r="M165" s="13" t="n"/>
-      <c r="N165" s="13" t="n"/>
-      <c r="O165" s="13" t="n"/>
+      <c r="B165" s="42" t="n"/>
+      <c r="C165" s="42" t="n"/>
+      <c r="D165" s="42" t="n"/>
+      <c r="E165" s="42" t="n"/>
+      <c r="F165" s="42" t="n"/>
+      <c r="G165" s="42" t="n"/>
+      <c r="H165" s="42" t="n"/>
+      <c r="I165" s="42" t="n"/>
+      <c r="J165" s="42" t="n"/>
+      <c r="K165" s="42" t="n"/>
+      <c r="L165" s="42" t="n"/>
+      <c r="M165" s="42" t="n"/>
+      <c r="N165" s="42" t="n"/>
+      <c r="O165" s="43" t="n"/>
     </row>
     <row r="166" ht="38" customHeight="1">
       <c r="A166" s="14" t="inlineStr">
@@ -10371,20 +10447,20 @@
           <t xml:space="preserve">  E.渲染与UI</t>
         </is>
       </c>
-      <c r="B169" s="11" t="n"/>
-      <c r="C169" s="11" t="n"/>
-      <c r="D169" s="11" t="n"/>
-      <c r="E169" s="11" t="n"/>
-      <c r="F169" s="11" t="n"/>
-      <c r="G169" s="11" t="n"/>
-      <c r="H169" s="11" t="n"/>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="11" t="n"/>
-      <c r="K169" s="11" t="n"/>
-      <c r="L169" s="11" t="n"/>
-      <c r="M169" s="11" t="n"/>
-      <c r="N169" s="11" t="n"/>
-      <c r="O169" s="11" t="n"/>
+      <c r="B169" s="42" t="n"/>
+      <c r="C169" s="42" t="n"/>
+      <c r="D169" s="42" t="n"/>
+      <c r="E169" s="42" t="n"/>
+      <c r="F169" s="42" t="n"/>
+      <c r="G169" s="42" t="n"/>
+      <c r="H169" s="42" t="n"/>
+      <c r="I169" s="42" t="n"/>
+      <c r="J169" s="42" t="n"/>
+      <c r="K169" s="42" t="n"/>
+      <c r="L169" s="42" t="n"/>
+      <c r="M169" s="42" t="n"/>
+      <c r="N169" s="42" t="n"/>
+      <c r="O169" s="43" t="n"/>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="12" t="inlineStr">
@@ -10392,20 +10468,20 @@
           <t xml:space="preserve">    ▸ E11.新手引导  [P6]</t>
         </is>
       </c>
-      <c r="B170" s="13" t="n"/>
-      <c r="C170" s="13" t="n"/>
-      <c r="D170" s="13" t="n"/>
-      <c r="E170" s="13" t="n"/>
-      <c r="F170" s="13" t="n"/>
-      <c r="G170" s="13" t="n"/>
-      <c r="H170" s="13" t="n"/>
-      <c r="I170" s="13" t="n"/>
-      <c r="J170" s="13" t="n"/>
-      <c r="K170" s="13" t="n"/>
-      <c r="L170" s="13" t="n"/>
-      <c r="M170" s="13" t="n"/>
-      <c r="N170" s="13" t="n"/>
-      <c r="O170" s="13" t="n"/>
+      <c r="B170" s="42" t="n"/>
+      <c r="C170" s="42" t="n"/>
+      <c r="D170" s="42" t="n"/>
+      <c r="E170" s="42" t="n"/>
+      <c r="F170" s="42" t="n"/>
+      <c r="G170" s="42" t="n"/>
+      <c r="H170" s="42" t="n"/>
+      <c r="I170" s="42" t="n"/>
+      <c r="J170" s="42" t="n"/>
+      <c r="K170" s="42" t="n"/>
+      <c r="L170" s="42" t="n"/>
+      <c r="M170" s="42" t="n"/>
+      <c r="N170" s="42" t="n"/>
+      <c r="O170" s="43" t="n"/>
     </row>
     <row r="171" ht="38" customHeight="1">
       <c r="A171" s="14" t="inlineStr">
@@ -10713,20 +10789,20 @@
           <t xml:space="preserve">  F.社交系统(V1.5)</t>
         </is>
       </c>
-      <c r="B175" s="11" t="n"/>
-      <c r="C175" s="11" t="n"/>
-      <c r="D175" s="11" t="n"/>
-      <c r="E175" s="11" t="n"/>
-      <c r="F175" s="11" t="n"/>
-      <c r="G175" s="11" t="n"/>
-      <c r="H175" s="11" t="n"/>
-      <c r="I175" s="11" t="n"/>
-      <c r="J175" s="11" t="n"/>
-      <c r="K175" s="11" t="n"/>
-      <c r="L175" s="11" t="n"/>
-      <c r="M175" s="11" t="n"/>
-      <c r="N175" s="11" t="n"/>
-      <c r="O175" s="11" t="n"/>
+      <c r="B175" s="42" t="n"/>
+      <c r="C175" s="42" t="n"/>
+      <c r="D175" s="42" t="n"/>
+      <c r="E175" s="42" t="n"/>
+      <c r="F175" s="42" t="n"/>
+      <c r="G175" s="42" t="n"/>
+      <c r="H175" s="42" t="n"/>
+      <c r="I175" s="42" t="n"/>
+      <c r="J175" s="42" t="n"/>
+      <c r="K175" s="42" t="n"/>
+      <c r="L175" s="42" t="n"/>
+      <c r="M175" s="42" t="n"/>
+      <c r="N175" s="42" t="n"/>
+      <c r="O175" s="43" t="n"/>
     </row>
     <row r="176" ht="38" customHeight="1">
       <c r="A176" s="14" t="inlineStr">
@@ -11184,20 +11260,20 @@
           <t xml:space="preserve">  G.养成变现(V1.5)</t>
         </is>
       </c>
-      <c r="B182" s="11" t="n"/>
-      <c r="C182" s="11" t="n"/>
-      <c r="D182" s="11" t="n"/>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="11" t="n"/>
-      <c r="G182" s="11" t="n"/>
-      <c r="H182" s="11" t="n"/>
-      <c r="I182" s="11" t="n"/>
-      <c r="J182" s="11" t="n"/>
-      <c r="K182" s="11" t="n"/>
-      <c r="L182" s="11" t="n"/>
-      <c r="M182" s="11" t="n"/>
-      <c r="N182" s="11" t="n"/>
-      <c r="O182" s="11" t="n"/>
+      <c r="B182" s="42" t="n"/>
+      <c r="C182" s="42" t="n"/>
+      <c r="D182" s="42" t="n"/>
+      <c r="E182" s="42" t="n"/>
+      <c r="F182" s="42" t="n"/>
+      <c r="G182" s="42" t="n"/>
+      <c r="H182" s="42" t="n"/>
+      <c r="I182" s="42" t="n"/>
+      <c r="J182" s="42" t="n"/>
+      <c r="K182" s="42" t="n"/>
+      <c r="L182" s="42" t="n"/>
+      <c r="M182" s="42" t="n"/>
+      <c r="N182" s="42" t="n"/>
+      <c r="O182" s="43" t="n"/>
     </row>
     <row r="183" ht="38" customHeight="1">
       <c r="A183" s="14" t="inlineStr">
@@ -11505,20 +11581,20 @@
           <t xml:space="preserve">  H.实时PvP(V2)</t>
         </is>
       </c>
-      <c r="B187" s="11" t="n"/>
-      <c r="C187" s="11" t="n"/>
-      <c r="D187" s="11" t="n"/>
-      <c r="E187" s="11" t="n"/>
-      <c r="F187" s="11" t="n"/>
-      <c r="G187" s="11" t="n"/>
-      <c r="H187" s="11" t="n"/>
-      <c r="I187" s="11" t="n"/>
-      <c r="J187" s="11" t="n"/>
-      <c r="K187" s="11" t="n"/>
-      <c r="L187" s="11" t="n"/>
-      <c r="M187" s="11" t="n"/>
-      <c r="N187" s="11" t="n"/>
-      <c r="O187" s="11" t="n"/>
+      <c r="B187" s="42" t="n"/>
+      <c r="C187" s="42" t="n"/>
+      <c r="D187" s="42" t="n"/>
+      <c r="E187" s="42" t="n"/>
+      <c r="F187" s="42" t="n"/>
+      <c r="G187" s="42" t="n"/>
+      <c r="H187" s="42" t="n"/>
+      <c r="I187" s="42" t="n"/>
+      <c r="J187" s="42" t="n"/>
+      <c r="K187" s="42" t="n"/>
+      <c r="L187" s="42" t="n"/>
+      <c r="M187" s="42" t="n"/>
+      <c r="N187" s="42" t="n"/>
+      <c r="O187" s="43" t="n"/>
     </row>
     <row r="188" ht="54" customHeight="1">
       <c r="A188" s="14" t="inlineStr">
@@ -11976,20 +12052,20 @@
           <t xml:space="preserve">  I.跨平台导出</t>
         </is>
       </c>
-      <c r="B194" s="11" t="n"/>
-      <c r="C194" s="11" t="n"/>
-      <c r="D194" s="11" t="n"/>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="11" t="n"/>
-      <c r="G194" s="11" t="n"/>
-      <c r="H194" s="11" t="n"/>
-      <c r="I194" s="11" t="n"/>
-      <c r="J194" s="11" t="n"/>
-      <c r="K194" s="11" t="n"/>
-      <c r="L194" s="11" t="n"/>
-      <c r="M194" s="11" t="n"/>
-      <c r="N194" s="11" t="n"/>
-      <c r="O194" s="11" t="n"/>
+      <c r="B194" s="42" t="n"/>
+      <c r="C194" s="42" t="n"/>
+      <c r="D194" s="42" t="n"/>
+      <c r="E194" s="42" t="n"/>
+      <c r="F194" s="42" t="n"/>
+      <c r="G194" s="42" t="n"/>
+      <c r="H194" s="42" t="n"/>
+      <c r="I194" s="42" t="n"/>
+      <c r="J194" s="42" t="n"/>
+      <c r="K194" s="42" t="n"/>
+      <c r="L194" s="42" t="n"/>
+      <c r="M194" s="42" t="n"/>
+      <c r="N194" s="42" t="n"/>
+      <c r="O194" s="43" t="n"/>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="12" t="inlineStr">
@@ -11997,20 +12073,20 @@
           <t xml:space="preserve">    ▸ I1.平台抽象层  [P8]</t>
         </is>
       </c>
-      <c r="B195" s="13" t="n"/>
-      <c r="C195" s="13" t="n"/>
-      <c r="D195" s="13" t="n"/>
-      <c r="E195" s="13" t="n"/>
-      <c r="F195" s="13" t="n"/>
-      <c r="G195" s="13" t="n"/>
-      <c r="H195" s="13" t="n"/>
-      <c r="I195" s="13" t="n"/>
-      <c r="J195" s="13" t="n"/>
-      <c r="K195" s="13" t="n"/>
-      <c r="L195" s="13" t="n"/>
-      <c r="M195" s="13" t="n"/>
-      <c r="N195" s="13" t="n"/>
-      <c r="O195" s="13" t="n"/>
+      <c r="B195" s="42" t="n"/>
+      <c r="C195" s="42" t="n"/>
+      <c r="D195" s="42" t="n"/>
+      <c r="E195" s="42" t="n"/>
+      <c r="F195" s="42" t="n"/>
+      <c r="G195" s="42" t="n"/>
+      <c r="H195" s="42" t="n"/>
+      <c r="I195" s="42" t="n"/>
+      <c r="J195" s="42" t="n"/>
+      <c r="K195" s="42" t="n"/>
+      <c r="L195" s="42" t="n"/>
+      <c r="M195" s="42" t="n"/>
+      <c r="N195" s="42" t="n"/>
+      <c r="O195" s="43" t="n"/>
     </row>
     <row r="196" ht="54" customHeight="1">
       <c r="A196" s="14" t="inlineStr">
@@ -12081,9 +12157,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O196" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O196" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12318,20 +12394,20 @@
           <t xml:space="preserve">  I.跨平台导出</t>
         </is>
       </c>
-      <c r="B200" s="11" t="n"/>
-      <c r="C200" s="11" t="n"/>
-      <c r="D200" s="11" t="n"/>
-      <c r="E200" s="11" t="n"/>
-      <c r="F200" s="11" t="n"/>
-      <c r="G200" s="11" t="n"/>
-      <c r="H200" s="11" t="n"/>
-      <c r="I200" s="11" t="n"/>
-      <c r="J200" s="11" t="n"/>
-      <c r="K200" s="11" t="n"/>
-      <c r="L200" s="11" t="n"/>
-      <c r="M200" s="11" t="n"/>
-      <c r="N200" s="11" t="n"/>
-      <c r="O200" s="11" t="n"/>
+      <c r="B200" s="42" t="n"/>
+      <c r="C200" s="42" t="n"/>
+      <c r="D200" s="42" t="n"/>
+      <c r="E200" s="42" t="n"/>
+      <c r="F200" s="42" t="n"/>
+      <c r="G200" s="42" t="n"/>
+      <c r="H200" s="42" t="n"/>
+      <c r="I200" s="42" t="n"/>
+      <c r="J200" s="42" t="n"/>
+      <c r="K200" s="42" t="n"/>
+      <c r="L200" s="42" t="n"/>
+      <c r="M200" s="42" t="n"/>
+      <c r="N200" s="42" t="n"/>
+      <c r="O200" s="43" t="n"/>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="12" t="inlineStr">
@@ -12339,20 +12415,20 @@
           <t xml:space="preserve">    ▸ I2.微信小游戏导出  [P8]</t>
         </is>
       </c>
-      <c r="B201" s="13" t="n"/>
-      <c r="C201" s="13" t="n"/>
-      <c r="D201" s="13" t="n"/>
-      <c r="E201" s="13" t="n"/>
-      <c r="F201" s="13" t="n"/>
-      <c r="G201" s="13" t="n"/>
-      <c r="H201" s="13" t="n"/>
-      <c r="I201" s="13" t="n"/>
-      <c r="J201" s="13" t="n"/>
-      <c r="K201" s="13" t="n"/>
-      <c r="L201" s="13" t="n"/>
-      <c r="M201" s="13" t="n"/>
-      <c r="N201" s="13" t="n"/>
-      <c r="O201" s="13" t="n"/>
+      <c r="B201" s="42" t="n"/>
+      <c r="C201" s="42" t="n"/>
+      <c r="D201" s="42" t="n"/>
+      <c r="E201" s="42" t="n"/>
+      <c r="F201" s="42" t="n"/>
+      <c r="G201" s="42" t="n"/>
+      <c r="H201" s="42" t="n"/>
+      <c r="I201" s="42" t="n"/>
+      <c r="J201" s="42" t="n"/>
+      <c r="K201" s="42" t="n"/>
+      <c r="L201" s="42" t="n"/>
+      <c r="M201" s="42" t="n"/>
+      <c r="N201" s="42" t="n"/>
+      <c r="O201" s="43" t="n"/>
     </row>
     <row r="202" ht="38" customHeight="1">
       <c r="A202" s="14" t="inlineStr">
@@ -12735,20 +12811,20 @@
           <t xml:space="preserve">  I.跨平台导出</t>
         </is>
       </c>
-      <c r="B207" s="11" t="n"/>
-      <c r="C207" s="11" t="n"/>
-      <c r="D207" s="11" t="n"/>
-      <c r="E207" s="11" t="n"/>
-      <c r="F207" s="11" t="n"/>
-      <c r="G207" s="11" t="n"/>
-      <c r="H207" s="11" t="n"/>
-      <c r="I207" s="11" t="n"/>
-      <c r="J207" s="11" t="n"/>
-      <c r="K207" s="11" t="n"/>
-      <c r="L207" s="11" t="n"/>
-      <c r="M207" s="11" t="n"/>
-      <c r="N207" s="11" t="n"/>
-      <c r="O207" s="11" t="n"/>
+      <c r="B207" s="42" t="n"/>
+      <c r="C207" s="42" t="n"/>
+      <c r="D207" s="42" t="n"/>
+      <c r="E207" s="42" t="n"/>
+      <c r="F207" s="42" t="n"/>
+      <c r="G207" s="42" t="n"/>
+      <c r="H207" s="42" t="n"/>
+      <c r="I207" s="42" t="n"/>
+      <c r="J207" s="42" t="n"/>
+      <c r="K207" s="42" t="n"/>
+      <c r="L207" s="42" t="n"/>
+      <c r="M207" s="42" t="n"/>
+      <c r="N207" s="42" t="n"/>
+      <c r="O207" s="43" t="n"/>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="12" t="inlineStr">
@@ -12756,20 +12832,20 @@
           <t xml:space="preserve">    ▸ I3.Steam导出  [P8]</t>
         </is>
       </c>
-      <c r="B208" s="13" t="n"/>
-      <c r="C208" s="13" t="n"/>
-      <c r="D208" s="13" t="n"/>
-      <c r="E208" s="13" t="n"/>
-      <c r="F208" s="13" t="n"/>
-      <c r="G208" s="13" t="n"/>
-      <c r="H208" s="13" t="n"/>
-      <c r="I208" s="13" t="n"/>
-      <c r="J208" s="13" t="n"/>
-      <c r="K208" s="13" t="n"/>
-      <c r="L208" s="13" t="n"/>
-      <c r="M208" s="13" t="n"/>
-      <c r="N208" s="13" t="n"/>
-      <c r="O208" s="13" t="n"/>
+      <c r="B208" s="42" t="n"/>
+      <c r="C208" s="42" t="n"/>
+      <c r="D208" s="42" t="n"/>
+      <c r="E208" s="42" t="n"/>
+      <c r="F208" s="42" t="n"/>
+      <c r="G208" s="42" t="n"/>
+      <c r="H208" s="42" t="n"/>
+      <c r="I208" s="42" t="n"/>
+      <c r="J208" s="42" t="n"/>
+      <c r="K208" s="42" t="n"/>
+      <c r="L208" s="42" t="n"/>
+      <c r="M208" s="42" t="n"/>
+      <c r="N208" s="42" t="n"/>
+      <c r="O208" s="43" t="n"/>
     </row>
     <row r="209" ht="38" customHeight="1">
       <c r="A209" s="14" t="inlineStr">
@@ -13077,20 +13153,20 @@
           <t xml:space="preserve">  I.跨平台导出</t>
         </is>
       </c>
-      <c r="B213" s="11" t="n"/>
-      <c r="C213" s="11" t="n"/>
-      <c r="D213" s="11" t="n"/>
-      <c r="E213" s="11" t="n"/>
-      <c r="F213" s="11" t="n"/>
-      <c r="G213" s="11" t="n"/>
-      <c r="H213" s="11" t="n"/>
-      <c r="I213" s="11" t="n"/>
-      <c r="J213" s="11" t="n"/>
-      <c r="K213" s="11" t="n"/>
-      <c r="L213" s="11" t="n"/>
-      <c r="M213" s="11" t="n"/>
-      <c r="N213" s="11" t="n"/>
-      <c r="O213" s="11" t="n"/>
+      <c r="B213" s="42" t="n"/>
+      <c r="C213" s="42" t="n"/>
+      <c r="D213" s="42" t="n"/>
+      <c r="E213" s="42" t="n"/>
+      <c r="F213" s="42" t="n"/>
+      <c r="G213" s="42" t="n"/>
+      <c r="H213" s="42" t="n"/>
+      <c r="I213" s="42" t="n"/>
+      <c r="J213" s="42" t="n"/>
+      <c r="K213" s="42" t="n"/>
+      <c r="L213" s="42" t="n"/>
+      <c r="M213" s="42" t="n"/>
+      <c r="N213" s="42" t="n"/>
+      <c r="O213" s="43" t="n"/>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="12" t="inlineStr">
@@ -13098,20 +13174,20 @@
           <t xml:space="preserve">    ▸ I4.安卓/谷歌商店导出  [P8]</t>
         </is>
       </c>
-      <c r="B214" s="13" t="n"/>
-      <c r="C214" s="13" t="n"/>
-      <c r="D214" s="13" t="n"/>
-      <c r="E214" s="13" t="n"/>
-      <c r="F214" s="13" t="n"/>
-      <c r="G214" s="13" t="n"/>
-      <c r="H214" s="13" t="n"/>
-      <c r="I214" s="13" t="n"/>
-      <c r="J214" s="13" t="n"/>
-      <c r="K214" s="13" t="n"/>
-      <c r="L214" s="13" t="n"/>
-      <c r="M214" s="13" t="n"/>
-      <c r="N214" s="13" t="n"/>
-      <c r="O214" s="13" t="n"/>
+      <c r="B214" s="42" t="n"/>
+      <c r="C214" s="42" t="n"/>
+      <c r="D214" s="42" t="n"/>
+      <c r="E214" s="42" t="n"/>
+      <c r="F214" s="42" t="n"/>
+      <c r="G214" s="42" t="n"/>
+      <c r="H214" s="42" t="n"/>
+      <c r="I214" s="42" t="n"/>
+      <c r="J214" s="42" t="n"/>
+      <c r="K214" s="42" t="n"/>
+      <c r="L214" s="42" t="n"/>
+      <c r="M214" s="42" t="n"/>
+      <c r="N214" s="42" t="n"/>
+      <c r="O214" s="43" t="n"/>
     </row>
     <row r="215" ht="38" customHeight="1">
       <c r="A215" s="14" t="inlineStr">
@@ -13524,6 +13600,11 @@
           <t>进度统计（自动计算）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -13890,6 +13971,16 @@
           <t>卡牌数据表（cardId 与代码一致）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="42" t="n"/>
+      <c r="G1" s="42" t="n"/>
+      <c r="H1" s="42" t="n"/>
+      <c r="I1" s="42" t="n"/>
+      <c r="J1" s="42" t="n"/>
+      <c r="K1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -15058,6 +15149,9 @@
           <t>核心数值配置（GDScript Const.gd）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -15460,6 +15554,7 @@
           <t>如何向AI提问开发（Godot版）</t>
         </is>
       </c>
+      <c r="B1" s="43" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
@@ -15602,6 +15697,13 @@
           <t>美术资源清单（Godot格式）</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="42" t="n"/>
+      <c r="G1" s="42" t="n"/>
+      <c r="H1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -17013,6 +17115,12 @@
           <t>决策日志与已知问题</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="42" t="n"/>
+      <c r="G1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -17057,6 +17165,12 @@
           <t xml:space="preserve">  ◆ 设计决策</t>
         </is>
       </c>
+      <c r="B3" s="42" t="n"/>
+      <c r="C3" s="42" t="n"/>
+      <c r="D3" s="42" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="43" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
@@ -17545,6 +17659,12 @@
           <t xml:space="preserve">  ◆ 已知问题</t>
         </is>
       </c>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="43" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -17875,6 +17995,11 @@
           <t>跨平台导出方案对比</t>
         </is>
       </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="42" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="43" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -13644,25 +13644,20 @@
           <t>P1 项目骨架</t>
         </is>
       </c>
-      <c r="B3" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P1"},0)))</f>
-        <v/>
-      </c>
-      <c r="C3" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P1"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D3" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P1"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E3" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P1"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F3" s="21">
-        <f>IF(B3&gt;0,C3/B3,0)</f>
-        <v/>
+      <c r="B3" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>0.6875</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -13671,25 +13666,20 @@
           <t>P2 游戏数据</t>
         </is>
       </c>
-      <c r="B4" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P2"},0)))</f>
-        <v/>
-      </c>
-      <c r="C4" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P2"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D4" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P2"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E4" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P2"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F4" s="23">
-        <f>IF(B4&gt;0,C4/B4,0)</f>
-        <v/>
+      <c r="B4" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
@@ -13698,25 +13688,20 @@
           <t>P3 核心战斗</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P3"},0)))</f>
-        <v/>
-      </c>
-      <c r="C5" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P3"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D5" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P3"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E5" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P3"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F5" s="21">
-        <f>IF(B5&gt;0,C5/B5,0)</f>
-        <v/>
+      <c r="B5" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -13725,25 +13710,20 @@
           <t>P4 扩展战斗</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P4"},0)))</f>
-        <v/>
-      </c>
-      <c r="C6" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P4"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D6" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P4"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E6" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P4"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>IF(B6&gt;0,C6/B6,0)</f>
-        <v/>
+      <c r="B6" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -13752,25 +13732,20 @@
           <t>P5 AI系统</t>
         </is>
       </c>
-      <c r="B7" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P5"},0)))</f>
-        <v/>
-      </c>
-      <c r="C7" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P5"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D7" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P5"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E7" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P5"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>IF(B7&gt;0,C7/B7,0)</f>
-        <v/>
+      <c r="B7" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
@@ -13779,25 +13754,20 @@
           <t>P6 渲染UI</t>
         </is>
       </c>
-      <c r="B8" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P6"},0)))</f>
-        <v/>
-      </c>
-      <c r="C8" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P6"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D8" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P6"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P6"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>IF(B8&gt;0,C8/B8,0)</f>
-        <v/>
+      <c r="B8" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
@@ -13806,25 +13776,20 @@
           <t>P0 环境搭建</t>
         </is>
       </c>
-      <c r="B9" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P7"},0)))</f>
-        <v/>
-      </c>
-      <c r="C9" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P7"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P7"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E9" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P7"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>IF(B9&gt;0,C9/B9,0)</f>
-        <v/>
+      <c r="B9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -13833,25 +13798,20 @@
           <t>P8 跨平台导出</t>
         </is>
       </c>
-      <c r="B10" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P8"},0)))</f>
-        <v/>
-      </c>
-      <c r="C10" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P8"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P8"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P8"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F10" s="23">
-        <f>IF(B10&gt;0,C10/B10,0)</f>
-        <v/>
+      <c r="B10" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0.0588</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -13860,25 +13820,20 @@
           <t>P9-14 社交养成</t>
         </is>
       </c>
-      <c r="B11" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P9","P10","P11","P12","P13","P14"},0)))</f>
-        <v/>
-      </c>
-      <c r="C11" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P9","P10","P11","P12","P13","P14"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P9","P10","P11","P12","P13","P14"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E11" s="20">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P9","P10","P11","P12","P13","P14"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>IF(B11&gt;0,C11/B11,0)</f>
-        <v/>
+      <c r="B11" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
@@ -13887,25 +13842,20 @@
           <t>P16-18 实时PvP</t>
         </is>
       </c>
-      <c r="B12" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P16","P17","P18"},0)))</f>
-        <v/>
-      </c>
-      <c r="C12" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P16","P17","P18"},0))*(2.开发主表!O3:O218="完成"))</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P16","P17","P18"},0))*(2.开发主表!O3:O218="进行中"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="22">
-        <f>SUMPRODUCT(--ISNUMBER(MATCH(2.开发主表!C3:C218,{"P16","P17","P18"},0))*(2.开发主表!O3:O218="待办"))</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>IF(B12&gt;0,C12/B12,0)</f>
-        <v/>
+      <c r="B12" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -13914,25 +13864,20 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B3:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="7">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="7">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="7">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>IF(C13&gt;0,C13/B13,0)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>0.0876</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -1741,9 +1741,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O6" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -1816,9 +1816,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O7" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2809,9 +2809,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O26" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O26" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2884,9 +2884,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O27" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O27" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -2959,9 +2959,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O28" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O28" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -3076,9 +3076,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O31" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O31" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -3151,9 +3151,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O32" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O32" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -3268,9 +3268,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O35" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O35" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -3343,9 +3343,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O36" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O36" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13648,16 +13648,16 @@
         <v>16</v>
       </c>
       <c r="C3" s="20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>0.6875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -13758,16 +13758,16 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
@@ -13868,16 +13868,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.0876</v>
+        <v>0.1533</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -1437,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O218"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3460,9 +3460,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O39" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O39" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3577,9 +3582,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O42" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O42" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3652,9 +3662,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O43" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O43" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3769,9 +3784,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O46" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O46" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3844,9 +3864,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O47" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O47" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3919,9 +3944,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O48" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O48" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3994,9 +4024,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O49" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O49" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4069,9 +4104,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O50" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O50" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4144,9 +4184,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O51" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O51" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -4261,9 +4306,14 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O54" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O54" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -13670,16 +13720,16 @@
         <v>10</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
@@ -13868,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.1533</v>
+        <v>0.2263</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -4428,9 +4428,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O57" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O57" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4545,9 +4545,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O60" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O60" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4620,9 +4620,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O61" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O61" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4695,9 +4695,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O62" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O62" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4770,9 +4770,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O63" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O63" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4887,9 +4887,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O66" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O66" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -4962,9 +4962,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O67" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O67" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5037,9 +5037,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O68" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O68" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5112,9 +5112,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O69" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O69" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5229,9 +5229,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O72" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O72" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5304,9 +5304,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O73" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O73" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5379,9 +5379,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O74" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O74" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5529,9 +5529,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O76" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O76" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5604,9 +5604,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O77" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O77" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13742,16 +13742,16 @@
         <v>14</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -13918,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.2263</v>
+        <v>0.3285</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -5454,9 +5454,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O75" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O75" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5721,9 +5721,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O80" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O80" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5796,9 +5796,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O81" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O81" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5871,9 +5871,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O82" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O82" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -5946,9 +5946,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O83" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O83" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6063,9 +6063,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O86" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O86" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6138,9 +6138,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O87" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O87" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6213,9 +6213,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O88" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O88" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6288,9 +6288,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O89" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O89" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6363,9 +6363,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O90" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O90" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6438,9 +6438,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O91" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O91" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6513,9 +6513,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O92" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O92" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6588,9 +6588,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O93" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O93" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6663,9 +6663,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O94" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O94" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6780,9 +6780,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O97" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O97" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6855,9 +6855,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O98" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O98" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -6930,9 +6930,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O99" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O99" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7005,9 +7005,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O100" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O100" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7080,9 +7080,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O101" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O101" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7155,9 +7155,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O102" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O102" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7272,9 +7272,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O105" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O105" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7347,9 +7347,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O106" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O106" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7464,9 +7464,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O109" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O109" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7539,9 +7539,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O110" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O110" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7656,9 +7656,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O113" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O113" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7731,9 +7731,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O114" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O114" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7806,9 +7806,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O115" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O115" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7923,9 +7923,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O118" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O118" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -7998,9 +7998,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O119" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O119" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13764,16 +13764,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D6" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -13918,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.3285</v>
+        <v>0.5401</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -8532,9 +8532,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O129" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O129" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8607,9 +8607,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O130" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O130" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8682,9 +8682,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O131" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O131" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8757,9 +8757,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O132" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O132" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8874,9 +8874,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O135" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O135" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8949,9 +8949,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O136" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O136" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9066,9 +9066,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O139" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O139" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9141,9 +9141,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O140" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O140" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9216,9 +9216,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O141" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O141" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9333,9 +9333,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O144" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O144" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9408,9 +9408,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O145" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O145" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9525,9 +9525,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O148" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O148" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9642,9 +9642,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O151" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O151" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9717,9 +9717,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O152" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O152" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9834,9 +9834,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O155" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O155" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -9951,9 +9951,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O158" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O158" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10026,9 +10026,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O159" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O159" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10143,9 +10143,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O162" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O162" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10218,9 +10218,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O163" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O163" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10335,9 +10335,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O166" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O166" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10410,9 +10410,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O167" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O167" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -10485,9 +10485,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O168" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O168" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13808,16 +13808,16 @@
         <v>30</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>0.1333</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
@@ -13918,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.5401</v>
+        <v>0.7007</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -8115,9 +8115,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O122" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O122" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8190,9 +8190,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O123" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O123" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8265,9 +8265,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O124" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O124" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8340,9 +8340,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O125" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O125" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -8415,9 +8415,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O126" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O126" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13786,16 +13786,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
@@ -13918,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.7007</v>
+        <v>0.7372</v>
       </c>
     </row>
   </sheetData>

--- a/宗门论道_Godot开发管理工具包.xlsx
+++ b/宗门论道_Godot开发管理工具包.xlsx
@@ -12282,9 +12282,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O197" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O197" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12357,9 +12357,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O198" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O198" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12432,9 +12432,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O199" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O199" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12549,9 +12549,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O202" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O202" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12624,9 +12624,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O203" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O203" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12699,9 +12699,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O204" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O204" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12774,9 +12774,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O205" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O205" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12849,9 +12849,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O206" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O206" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -12966,9 +12966,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O209" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O209" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13041,9 +13041,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O210" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O210" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13116,9 +13116,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O211" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O211" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13191,9 +13191,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O212" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O212" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13308,9 +13308,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O215" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O215" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13383,9 +13383,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O216" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O216" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13458,9 +13458,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O217" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O217" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13533,9 +13533,9 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="O218" s="17" t="inlineStr">
-        <is>
-          <t>待办</t>
+      <c r="O218" s="44" t="inlineStr">
+        <is>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -13852,16 +13852,16 @@
         <v>17</v>
       </c>
       <c r="C10" s="22" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.0588</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -13918,16 +13918,16 @@
         <v>137</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.7372</v>
+        <v>0.854</v>
       </c>
     </row>
   </sheetData>
